--- a/filesystem/MarketingOps/Org/client_services_account_transition_log.xlsx
+++ b/filesystem/MarketingOps/Org/client_services_account_transition_log.xlsx
@@ -121,7 +121,7 @@
       <sz val="9.5"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -185,8 +185,18 @@
         <bgColor rgb="00FFFBEB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F1F5F9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="15">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -299,11 +309,114 @@
         <color rgb="00CBD5E1"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="000284C7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <right/>
+      <bottom style="medium">
+        <color rgb="000284C7"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <bottom/>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -491,6 +604,41 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="11" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -800,7 +948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J72"/>
+  <dimension ref="A1:J65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -816,20 +964,20 @@
   </cols>
   <sheetData>
     <row r="1" ht="38" customHeight="1">
-      <c r="A1" s="21" t="inlineStr">
+      <c r="A1" s="83" t="inlineStr">
         <is>
           <t>THORNFIELD LIFE SCIENCES MARKETING — Inherited Accounts &amp; Client Services Transition Log</t>
         </is>
       </c>
-      <c r="B1" s="21" t="n"/>
-      <c r="C1" s="21" t="n"/>
-      <c r="D1" s="21" t="n"/>
-      <c r="E1" s="21" t="n"/>
-      <c r="F1" s="21" t="n"/>
-      <c r="G1" s="21" t="n"/>
-      <c r="H1" s="21" t="n"/>
-      <c r="I1" s="21" t="n"/>
-      <c r="J1" s="21" t="n"/>
+      <c r="B1" s="69" t="n"/>
+      <c r="C1" s="69" t="n"/>
+      <c r="D1" s="69" t="n"/>
+      <c r="E1" s="69" t="n"/>
+      <c r="F1" s="69" t="n"/>
+      <c r="G1" s="69" t="n"/>
+      <c r="H1" s="69" t="n"/>
+      <c r="I1" s="69" t="n"/>
+      <c r="J1" s="69" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="22" t="inlineStr">
@@ -837,19 +985,19 @@
           <t>File:</t>
         </is>
       </c>
-      <c r="B2" s="23" t="inlineStr">
+      <c r="B2" s="84" t="inlineStr">
         <is>
           <t>/MarketingOps/Org/client_services_account_transition_log.xlsx</t>
         </is>
       </c>
-      <c r="C2" s="23" t="n"/>
-      <c r="D2" s="23" t="n"/>
-      <c r="E2" s="23" t="n"/>
-      <c r="F2" s="23" t="n"/>
-      <c r="G2" s="23" t="n"/>
-      <c r="H2" s="23" t="n"/>
-      <c r="I2" s="23" t="n"/>
-      <c r="J2" s="23" t="n"/>
+      <c r="C2" s="70" t="n"/>
+      <c r="D2" s="70" t="n"/>
+      <c r="E2" s="70" t="n"/>
+      <c r="F2" s="70" t="n"/>
+      <c r="G2" s="70" t="n"/>
+      <c r="H2" s="70" t="n"/>
+      <c r="I2" s="70" t="n"/>
+      <c r="J2" s="71" t="n"/>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
@@ -857,19 +1005,12 @@
           <t>Owner:</t>
         </is>
       </c>
-      <c r="B3" s="25" t="inlineStr">
+      <c r="B3" s="85" t="inlineStr">
         <is>
           <t>Sofia Bergen, Director, Client Strategy (formerly Bramwell)</t>
         </is>
       </c>
-      <c r="C3" s="25" t="n"/>
-      <c r="D3" s="25" t="n"/>
-      <c r="E3" s="25" t="n"/>
-      <c r="F3" s="25" t="n"/>
-      <c r="G3" s="25" t="n"/>
-      <c r="H3" s="25" t="n"/>
-      <c r="I3" s="25" t="n"/>
-      <c r="J3" s="25" t="n"/>
+      <c r="J3" s="72" t="n"/>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
@@ -877,19 +1018,12 @@
           <t>Scope:</t>
         </is>
       </c>
-      <c r="B4" s="25" t="inlineStr">
+      <c r="B4" s="85" t="inlineStr">
         <is>
           <t>Ex-Bramwell client roster migrated into Thornfield's ERPNext instance at 9/1/2025 close; ownership realignment and legacy-MSA disposition tracked here.</t>
         </is>
       </c>
-      <c r="C4" s="25" t="n"/>
-      <c r="D4" s="25" t="n"/>
-      <c r="E4" s="25" t="n"/>
-      <c r="F4" s="25" t="n"/>
-      <c r="G4" s="25" t="n"/>
-      <c r="H4" s="25" t="n"/>
-      <c r="I4" s="25" t="n"/>
-      <c r="J4" s="25" t="n"/>
+      <c r="J4" s="72" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="26" t="inlineStr">
@@ -902,14 +1036,14 @@
           <t>USD ($#,##0). Dates: MM/DD/YYYY.</t>
         </is>
       </c>
-      <c r="C5" s="27" t="n"/>
-      <c r="D5" s="27" t="n"/>
-      <c r="E5" s="27" t="n"/>
-      <c r="F5" s="27" t="n"/>
-      <c r="G5" s="27" t="n"/>
-      <c r="H5" s="27" t="n"/>
-      <c r="I5" s="27" t="n"/>
-      <c r="J5" s="27" t="n"/>
+      <c r="C5" s="73" t="n"/>
+      <c r="D5" s="73" t="n"/>
+      <c r="E5" s="73" t="n"/>
+      <c r="F5" s="73" t="n"/>
+      <c r="G5" s="73" t="n"/>
+      <c r="H5" s="73" t="n"/>
+      <c r="I5" s="73" t="n"/>
+      <c r="J5" s="74" t="n"/>
     </row>
     <row r="6" ht="12" customHeight="1"/>
     <row r="7" ht="28" customHeight="1">
@@ -1920,15 +2054,47 @@
           <t>CUST-2025-0130</t>
         </is>
       </c>
-      <c r="B29" s="39" t="n"/>
-      <c r="C29" s="39" t="n"/>
-      <c r="D29" s="39" t="n"/>
-      <c r="E29" s="39" t="n"/>
-      <c r="F29" s="48" t="n"/>
-      <c r="G29" s="48" t="n"/>
-      <c r="H29" s="39" t="n"/>
-      <c r="I29" s="39" t="n"/>
-      <c r="J29" s="39" t="n"/>
+      <c r="B29" s="40" t="inlineStr">
+        <is>
+          <t>Belmont Assay Systems</t>
+        </is>
+      </c>
+      <c r="C29" s="41" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+      <c r="D29" s="42" t="inlineStr">
+        <is>
+          <t>Katya Ovaskainen</t>
+        </is>
+      </c>
+      <c r="E29" s="42" t="inlineStr">
+        <is>
+          <t>Vanessa Trotter</t>
+        </is>
+      </c>
+      <c r="F29" s="43" t="n">
+        <v>45078</v>
+      </c>
+      <c r="G29" s="43" t="n">
+        <v>45808</v>
+      </c>
+      <c r="H29" s="47" t="inlineStr">
+        <is>
+          <t>% of managed spend</t>
+        </is>
+      </c>
+      <c r="I29" s="37" t="inlineStr">
+        <is>
+          <t>Transitioned</t>
+        </is>
+      </c>
+      <c r="J29" s="45" t="inlineStr">
+        <is>
+          <t>Ongoing under Thornfield standard billing.</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="31" t="inlineStr">
@@ -1936,15 +2102,47 @@
           <t>CUST-2025-0133</t>
         </is>
       </c>
-      <c r="B30" s="31" t="n"/>
-      <c r="C30" s="31" t="n"/>
-      <c r="D30" s="31" t="n"/>
-      <c r="E30" s="31" t="n"/>
-      <c r="F30" s="49" t="n"/>
-      <c r="G30" s="49" t="n"/>
-      <c r="H30" s="31" t="n"/>
-      <c r="I30" s="31" t="n"/>
-      <c r="J30" s="31" t="n"/>
+      <c r="B30" s="32" t="inlineStr">
+        <is>
+          <t>Chatfield Diagnostics</t>
+        </is>
+      </c>
+      <c r="C30" s="33" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+      <c r="D30" s="34" t="inlineStr">
+        <is>
+          <t>Diego Prasetya</t>
+        </is>
+      </c>
+      <c r="E30" s="34" t="inlineStr">
+        <is>
+          <t>Anika Whitworth</t>
+        </is>
+      </c>
+      <c r="F30" s="35" t="n">
+        <v>45179</v>
+      </c>
+      <c r="G30" s="35" t="n">
+        <v>45909</v>
+      </c>
+      <c r="H30" s="36" t="inlineStr">
+        <is>
+          <t>% of managed spend</t>
+        </is>
+      </c>
+      <c r="I30" s="37" t="inlineStr">
+        <is>
+          <t>Transitioned</t>
+        </is>
+      </c>
+      <c r="J30" s="38" t="inlineStr">
+        <is>
+          <t>Ongoing under Thornfield standard billing.</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="39" t="inlineStr">
@@ -1952,15 +2150,47 @@
           <t>CUST-2025-0136</t>
         </is>
       </c>
-      <c r="B31" s="39" t="n"/>
-      <c r="C31" s="39" t="n"/>
-      <c r="D31" s="39" t="n"/>
-      <c r="E31" s="39" t="n"/>
-      <c r="F31" s="48" t="n"/>
-      <c r="G31" s="48" t="n"/>
-      <c r="H31" s="39" t="n"/>
-      <c r="I31" s="39" t="n"/>
-      <c r="J31" s="39" t="n"/>
+      <c r="B31" s="40" t="inlineStr">
+        <is>
+          <t>Deepwater Bioanalytics</t>
+        </is>
+      </c>
+      <c r="C31" s="41" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+      <c r="D31" s="42" t="inlineStr">
+        <is>
+          <t>Emeka Balogun</t>
+        </is>
+      </c>
+      <c r="E31" s="42" t="inlineStr">
+        <is>
+          <t>Cyrus Delacroix</t>
+        </is>
+      </c>
+      <c r="F31" s="43" t="n">
+        <v>45306</v>
+      </c>
+      <c r="G31" s="43" t="n">
+        <v>46036</v>
+      </c>
+      <c r="H31" s="47" t="inlineStr">
+        <is>
+          <t>% of managed spend</t>
+        </is>
+      </c>
+      <c r="I31" s="37" t="inlineStr">
+        <is>
+          <t>Transitioned</t>
+        </is>
+      </c>
+      <c r="J31" s="45" t="inlineStr">
+        <is>
+          <t>Ongoing under Thornfield standard billing.</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="31" t="inlineStr">
@@ -1968,15 +2198,45 @@
           <t>CUST-2025-0139</t>
         </is>
       </c>
-      <c r="B32" s="31" t="n"/>
-      <c r="C32" s="31" t="n"/>
-      <c r="D32" s="31" t="n"/>
-      <c r="E32" s="31" t="n"/>
-      <c r="F32" s="49" t="n"/>
-      <c r="G32" s="49" t="n"/>
-      <c r="H32" s="31" t="n"/>
-      <c r="I32" s="31" t="n"/>
-      <c r="J32" s="31" t="n"/>
+      <c r="B32" s="32" t="inlineStr">
+        <is>
+          <t>Elmswood Reagent Labs</t>
+        </is>
+      </c>
+      <c r="C32" s="33" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+      <c r="D32" s="34" t="inlineStr">
+        <is>
+          <t>Katya Ovaskainen</t>
+        </is>
+      </c>
+      <c r="E32" s="34" t="inlineStr">
+        <is>
+          <t>Reid Alderman</t>
+        </is>
+      </c>
+      <c r="F32" s="35" t="n">
+        <v>45250</v>
+      </c>
+      <c r="G32" s="35" t="n">
+        <v>45980</v>
+      </c>
+      <c r="H32" s="36" t="n">
+        <v>5400</v>
+      </c>
+      <c r="I32" s="37" t="inlineStr">
+        <is>
+          <t>Transitioned</t>
+        </is>
+      </c>
+      <c r="J32" s="38" t="inlineStr">
+        <is>
+          <t>Ongoing under Thornfield standard billing.</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="39" t="inlineStr">
@@ -1984,15 +2244,47 @@
           <t>CUST-2025-0145</t>
         </is>
       </c>
-      <c r="B33" s="39" t="n"/>
-      <c r="C33" s="39" t="n"/>
-      <c r="D33" s="39" t="n"/>
-      <c r="E33" s="39" t="n"/>
-      <c r="F33" s="48" t="n"/>
-      <c r="G33" s="48" t="n"/>
-      <c r="H33" s="39" t="n"/>
-      <c r="I33" s="39" t="n"/>
-      <c r="J33" s="39" t="n"/>
+      <c r="B33" s="40" t="inlineStr">
+        <is>
+          <t>Grantham Molecular Sciences</t>
+        </is>
+      </c>
+      <c r="C33" s="41" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+      <c r="D33" s="42" t="inlineStr">
+        <is>
+          <t>Diego Prasetya</t>
+        </is>
+      </c>
+      <c r="E33" s="42" t="inlineStr">
+        <is>
+          <t>Sofia Bergen</t>
+        </is>
+      </c>
+      <c r="F33" s="43" t="n">
+        <v>45352</v>
+      </c>
+      <c r="G33" s="43" t="n">
+        <v>46081</v>
+      </c>
+      <c r="H33" s="47" t="inlineStr">
+        <is>
+          <t>% of managed spend</t>
+        </is>
+      </c>
+      <c r="I33" s="37" t="inlineStr">
+        <is>
+          <t>Transitioned</t>
+        </is>
+      </c>
+      <c r="J33" s="45" t="inlineStr">
+        <is>
+          <t>Ongoing under Thornfield standard billing.</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="31" t="inlineStr">
@@ -2046,15 +2338,45 @@
           <t>CUST-2025-0154</t>
         </is>
       </c>
-      <c r="B35" s="39" t="n"/>
-      <c r="C35" s="39" t="n"/>
-      <c r="D35" s="39" t="n"/>
-      <c r="E35" s="39" t="n"/>
-      <c r="F35" s="48" t="n"/>
-      <c r="G35" s="48" t="n"/>
-      <c r="H35" s="39" t="n"/>
-      <c r="I35" s="39" t="n"/>
-      <c r="J35" s="39" t="n"/>
+      <c r="B35" s="40" t="inlineStr">
+        <is>
+          <t>Jarrow Cell Culture Systems</t>
+        </is>
+      </c>
+      <c r="C35" s="41" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+      <c r="D35" s="42" t="inlineStr">
+        <is>
+          <t>Emeka Balogun</t>
+        </is>
+      </c>
+      <c r="E35" s="42" t="inlineStr">
+        <is>
+          <t>Vanessa Trotter</t>
+        </is>
+      </c>
+      <c r="F35" s="43" t="n">
+        <v>45143</v>
+      </c>
+      <c r="G35" s="43" t="n">
+        <v>45873</v>
+      </c>
+      <c r="H35" s="47" t="n">
+        <v>4200</v>
+      </c>
+      <c r="I35" s="37" t="inlineStr">
+        <is>
+          <t>Transitioned</t>
+        </is>
+      </c>
+      <c r="J35" s="45" t="inlineStr">
+        <is>
+          <t>Ongoing under Thornfield standard billing.</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="31" t="inlineStr">
@@ -2067,14 +2389,42 @@
           <t>Kilbourne Genomics</t>
         </is>
       </c>
-      <c r="C36" s="32" t="n"/>
-      <c r="D36" s="32" t="n"/>
-      <c r="E36" s="32" t="n"/>
-      <c r="F36" s="50" t="n"/>
-      <c r="G36" s="50" t="n"/>
-      <c r="H36" s="32" t="n"/>
-      <c r="I36" s="32" t="n"/>
-      <c r="J36" s="32" t="n"/>
+      <c r="C36" s="33" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+      <c r="D36" s="34" t="inlineStr">
+        <is>
+          <t>Katya Ovaskainen</t>
+        </is>
+      </c>
+      <c r="E36" s="34" t="inlineStr">
+        <is>
+          <t>Anika Whitworth</t>
+        </is>
+      </c>
+      <c r="F36" s="35" t="n">
+        <v>45392</v>
+      </c>
+      <c r="G36" s="35" t="n">
+        <v>46121</v>
+      </c>
+      <c r="H36" s="36" t="inlineStr">
+        <is>
+          <t>% of managed spend</t>
+        </is>
+      </c>
+      <c r="I36" s="37" t="inlineStr">
+        <is>
+          <t>Transitioned</t>
+        </is>
+      </c>
+      <c r="J36" s="38" t="inlineStr">
+        <is>
+          <t>Ongoing under Thornfield standard billing.</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="39" t="inlineStr">
@@ -2087,14 +2437,42 @@
           <t>Marchmont Diagnostics</t>
         </is>
       </c>
-      <c r="C37" s="40" t="n"/>
-      <c r="D37" s="40" t="n"/>
-      <c r="E37" s="40" t="n"/>
-      <c r="F37" s="51" t="n"/>
-      <c r="G37" s="51" t="n"/>
-      <c r="H37" s="40" t="n"/>
-      <c r="I37" s="40" t="n"/>
-      <c r="J37" s="40" t="n"/>
+      <c r="C37" s="41" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+      <c r="D37" s="42" t="inlineStr">
+        <is>
+          <t>Diego Prasetya</t>
+        </is>
+      </c>
+      <c r="E37" s="42" t="inlineStr">
+        <is>
+          <t>Cyrus Delacroix</t>
+        </is>
+      </c>
+      <c r="F37" s="43" t="n">
+        <v>45272</v>
+      </c>
+      <c r="G37" s="43" t="n">
+        <v>46002</v>
+      </c>
+      <c r="H37" s="47" t="inlineStr">
+        <is>
+          <t>% of managed spend</t>
+        </is>
+      </c>
+      <c r="I37" s="37" t="inlineStr">
+        <is>
+          <t>Transitioned</t>
+        </is>
+      </c>
+      <c r="J37" s="45" t="inlineStr">
+        <is>
+          <t>Ongoing under Thornfield standard billing.</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="31" t="inlineStr">
@@ -2239,94 +2617,94 @@
       </c>
     </row>
     <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="39" t="inlineStr">
-        <is>
-          <t>CUST-2025-0184</t>
-        </is>
-      </c>
-      <c r="B41" s="40" t="inlineStr">
-        <is>
-          <t>Selwood Cell Systems</t>
-        </is>
-      </c>
-      <c r="C41" s="41" t="inlineStr">
-        <is>
-          <t>Inherited — Bramwell</t>
-        </is>
-      </c>
-      <c r="D41" s="42" t="inlineStr">
-        <is>
-          <t>Katya Ovaskainen</t>
-        </is>
-      </c>
-      <c r="E41" s="42" t="inlineStr">
-        <is>
-          <t>Anika Whitworth</t>
-        </is>
-      </c>
-      <c r="F41" s="43" t="n">
-        <v>45422</v>
-      </c>
-      <c r="G41" s="43" t="n">
-        <v>46152</v>
-      </c>
-      <c r="H41" s="44" t="n">
-        <v>3600</v>
+      <c r="A41" s="31" t="inlineStr">
+        <is>
+          <t>CUST-2025-0187</t>
+        </is>
+      </c>
+      <c r="B41" s="32" t="inlineStr">
+        <is>
+          <t>Trentham Diagnostics</t>
+        </is>
+      </c>
+      <c r="C41" s="33" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+      <c r="D41" s="34" t="inlineStr">
+        <is>
+          <t>Emeka Balogun</t>
+        </is>
+      </c>
+      <c r="E41" s="34" t="inlineStr">
+        <is>
+          <t>Reid Alderman</t>
+        </is>
+      </c>
+      <c r="F41" s="35" t="n">
+        <v>45517</v>
+      </c>
+      <c r="G41" s="35" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H41" s="36" t="inlineStr">
+        <is>
+          <t>% of managed spend</t>
+        </is>
       </c>
       <c r="I41" s="37" t="inlineStr">
         <is>
           <t>Transitioned</t>
         </is>
       </c>
-      <c r="J41" s="45" t="inlineStr">
+      <c r="J41" s="38" t="inlineStr">
         <is>
           <t>Ongoing under Thornfield standard billing.</t>
         </is>
       </c>
     </row>
     <row r="42" ht="22" customHeight="1">
-      <c r="A42" s="31" t="inlineStr">
-        <is>
-          <t>CUST-2025-0187</t>
-        </is>
-      </c>
-      <c r="B42" s="32" t="inlineStr">
-        <is>
-          <t>Trentham Diagnostics</t>
-        </is>
-      </c>
-      <c r="C42" s="33" t="inlineStr">
-        <is>
-          <t>Inherited — Bramwell</t>
-        </is>
-      </c>
-      <c r="D42" s="34" t="inlineStr">
-        <is>
-          <t>Emeka Balogun</t>
-        </is>
-      </c>
-      <c r="E42" s="34" t="inlineStr">
-        <is>
-          <t>Reid Alderman</t>
-        </is>
-      </c>
-      <c r="F42" s="35" t="n">
-        <v>45517</v>
-      </c>
-      <c r="G42" s="35" t="n">
-        <v>46247</v>
-      </c>
-      <c r="H42" s="36" t="inlineStr">
-        <is>
-          <t>% of managed spend</t>
-        </is>
+      <c r="A42" s="39" t="inlineStr">
+        <is>
+          <t>CUST-2025-0190</t>
+        </is>
+      </c>
+      <c r="B42" s="40" t="inlineStr">
+        <is>
+          <t>Ullswater Genomics</t>
+        </is>
+      </c>
+      <c r="C42" s="41" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+      <c r="D42" s="42" t="inlineStr">
+        <is>
+          <t>Nora Fitzhugh</t>
+        </is>
+      </c>
+      <c r="E42" s="42" t="inlineStr">
+        <is>
+          <t>Sofia Bergen</t>
+        </is>
+      </c>
+      <c r="F42" s="43" t="n">
+        <v>45612</v>
+      </c>
+      <c r="G42" s="43" t="n">
+        <v>46342</v>
+      </c>
+      <c r="H42" s="44" t="n">
+        <v>3000</v>
       </c>
       <c r="I42" s="37" t="inlineStr">
         <is>
           <t>Transitioned</t>
         </is>
       </c>
-      <c r="J42" s="38" t="inlineStr">
+      <c r="J42" s="45" t="inlineStr">
         <is>
           <t>Ongoing under Thornfield standard billing.</t>
         </is>
@@ -2335,12 +2713,12 @@
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="39" t="inlineStr">
         <is>
-          <t>CUST-2025-0190</t>
+          <t>CUST-2025-0196</t>
         </is>
       </c>
       <c r="B43" s="40" t="inlineStr">
         <is>
-          <t>Ullswater Genomics</t>
+          <t>Whitmore Assay Group</t>
         </is>
       </c>
       <c r="C43" s="41" t="inlineStr">
@@ -2350,123 +2728,123 @@
       </c>
       <c r="D43" s="42" t="inlineStr">
         <is>
+          <t>Katya Ovaskainen</t>
+        </is>
+      </c>
+      <c r="E43" s="42" t="inlineStr">
+        <is>
+          <t>Vanessa Trotter</t>
+        </is>
+      </c>
+      <c r="F43" s="43" t="n">
+        <v>45434</v>
+      </c>
+      <c r="G43" s="43" t="n">
+        <v>46164</v>
+      </c>
+      <c r="H43" s="44" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I43" s="37" t="inlineStr">
+        <is>
+          <t>Transitioned</t>
+        </is>
+      </c>
+      <c r="J43" s="45" t="inlineStr">
+        <is>
+          <t>Ongoing under Thornfield standard billing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="39" t="inlineStr">
+        <is>
+          <t>CUST-2025-0207</t>
+        </is>
+      </c>
+      <c r="B44" s="40" t="inlineStr">
+        <is>
+          <t>Ainsworth Bioanalytics</t>
+        </is>
+      </c>
+      <c r="C44" s="41" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+      <c r="D44" s="42" t="inlineStr">
+        <is>
+          <t>Emeka Balogun</t>
+        </is>
+      </c>
+      <c r="E44" s="42" t="inlineStr">
+        <is>
+          <t>Reid Alderman</t>
+        </is>
+      </c>
+      <c r="F44" s="43" t="n">
+        <v>45024</v>
+      </c>
+      <c r="G44" s="43" t="n">
+        <v>45755</v>
+      </c>
+      <c r="H44" s="47" t="inlineStr">
+        <is>
+          <t>% of managed spend</t>
+        </is>
+      </c>
+      <c r="I44" s="37" t="inlineStr">
+        <is>
+          <t>Transitioned</t>
+        </is>
+      </c>
+      <c r="J44" s="45" t="inlineStr">
+        <is>
+          <t>Ongoing under Thornfield standard billing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="31" t="inlineStr">
+        <is>
+          <t>CUST-2025-0210</t>
+        </is>
+      </c>
+      <c r="B45" s="32" t="inlineStr">
+        <is>
+          <t>Blackthorn Reagent Systems</t>
+        </is>
+      </c>
+      <c r="C45" s="33" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+      <c r="D45" s="34" t="inlineStr">
+        <is>
           <t>Nora Fitzhugh</t>
         </is>
       </c>
-      <c r="E43" s="42" t="inlineStr">
+      <c r="E45" s="34" t="inlineStr">
         <is>
           <t>Sofia Bergen</t>
         </is>
       </c>
-      <c r="F43" s="43" t="n">
-        <v>45612</v>
-      </c>
-      <c r="G43" s="43" t="n">
-        <v>46342</v>
-      </c>
-      <c r="H43" s="44" t="n">
-        <v>3000</v>
-      </c>
-      <c r="I43" s="37" t="inlineStr">
+      <c r="F45" s="35" t="n">
+        <v>45118</v>
+      </c>
+      <c r="G45" s="35" t="n">
+        <v>45849</v>
+      </c>
+      <c r="H45" s="46" t="n">
+        <v>6900</v>
+      </c>
+      <c r="I45" s="37" t="inlineStr">
         <is>
           <t>Transitioned</t>
         </is>
       </c>
-      <c r="J43" s="45" t="inlineStr">
-        <is>
-          <t>Ongoing under Thornfield standard billing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="31" t="inlineStr">
-        <is>
-          <t>CUST-2025-0193</t>
-        </is>
-      </c>
-      <c r="B44" s="32" t="inlineStr">
-        <is>
-          <t>Vantage Bioinstruments</t>
-        </is>
-      </c>
-      <c r="C44" s="33" t="inlineStr">
-        <is>
-          <t>Inherited — Bramwell</t>
-        </is>
-      </c>
-      <c r="D44" s="34" t="inlineStr">
-        <is>
-          <t>Diego Prasetya</t>
-        </is>
-      </c>
-      <c r="E44" s="34" t="inlineStr">
-        <is>
-          <t>Cyrus Delacroix</t>
-        </is>
-      </c>
-      <c r="F44" s="35" t="n">
-        <v>45341</v>
-      </c>
-      <c r="G44" s="35" t="n">
-        <v>46072</v>
-      </c>
-      <c r="H44" s="36" t="inlineStr">
-        <is>
-          <t>% of managed spend</t>
-        </is>
-      </c>
-      <c r="I44" s="37" t="inlineStr">
-        <is>
-          <t>Transitioned</t>
-        </is>
-      </c>
-      <c r="J44" s="38" t="inlineStr">
-        <is>
-          <t>Ongoing under Thornfield standard billing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="22" customHeight="1">
-      <c r="A45" s="39" t="inlineStr">
-        <is>
-          <t>CUST-2025-0196</t>
-        </is>
-      </c>
-      <c r="B45" s="40" t="inlineStr">
-        <is>
-          <t>Whitmore Assay Group</t>
-        </is>
-      </c>
-      <c r="C45" s="41" t="inlineStr">
-        <is>
-          <t>Inherited — Bramwell</t>
-        </is>
-      </c>
-      <c r="D45" s="42" t="inlineStr">
-        <is>
-          <t>Katya Ovaskainen</t>
-        </is>
-      </c>
-      <c r="E45" s="42" t="inlineStr">
-        <is>
-          <t>Vanessa Trotter</t>
-        </is>
-      </c>
-      <c r="F45" s="43" t="n">
-        <v>45434</v>
-      </c>
-      <c r="G45" s="43" t="n">
-        <v>46164</v>
-      </c>
-      <c r="H45" s="44" t="n">
-        <v>1300</v>
-      </c>
-      <c r="I45" s="37" t="inlineStr">
-        <is>
-          <t>Transitioned</t>
-        </is>
-      </c>
-      <c r="J45" s="45" t="inlineStr">
+      <c r="J45" s="38" t="inlineStr">
         <is>
           <t>Ongoing under Thornfield standard billing.</t>
         </is>
@@ -2475,12 +2853,12 @@
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="31" t="inlineStr">
         <is>
-          <t>CUST-2025-0204</t>
+          <t>CUST-2025-0216</t>
         </is>
       </c>
       <c r="B46" s="32" t="inlineStr">
         <is>
-          <t>Yardley Molecular Diagnostics</t>
+          <t>Drayton Cell Culture</t>
         </is>
       </c>
       <c r="C46" s="33" t="inlineStr">
@@ -2495,17 +2873,17 @@
       </c>
       <c r="E46" s="34" t="inlineStr">
         <is>
-          <t>Anika Whitworth</t>
+          <t>Vanessa Trotter</t>
         </is>
       </c>
       <c r="F46" s="35" t="n">
-        <v>44931</v>
+        <v>44943</v>
       </c>
       <c r="G46" s="35" t="n">
-        <v>45662</v>
+        <v>45674</v>
       </c>
       <c r="H46" s="46" t="n">
-        <v>15800</v>
+        <v>4400</v>
       </c>
       <c r="I46" s="37" t="inlineStr">
         <is>
@@ -2519,48 +2897,46 @@
       </c>
     </row>
     <row r="47" ht="22" customHeight="1">
-      <c r="A47" s="39" t="inlineStr">
-        <is>
-          <t>CUST-2025-0207</t>
-        </is>
-      </c>
-      <c r="B47" s="40" t="inlineStr">
-        <is>
-          <t>Ainsworth Bioanalytics</t>
-        </is>
-      </c>
-      <c r="C47" s="41" t="inlineStr">
-        <is>
-          <t>Inherited — Bramwell</t>
-        </is>
-      </c>
-      <c r="D47" s="42" t="inlineStr">
-        <is>
-          <t>Emeka Balogun</t>
-        </is>
-      </c>
-      <c r="E47" s="42" t="inlineStr">
+      <c r="A47" s="31" t="inlineStr">
+        <is>
+          <t>CUST-2025-0222</t>
+        </is>
+      </c>
+      <c r="B47" s="32" t="inlineStr">
+        <is>
+          <t>Foxhaven Genomic Analytics</t>
+        </is>
+      </c>
+      <c r="C47" s="33" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+      <c r="D47" s="34" t="inlineStr">
+        <is>
+          <t>Nora Fitzhugh</t>
+        </is>
+      </c>
+      <c r="E47" s="34" t="inlineStr">
         <is>
           <t>Reid Alderman</t>
         </is>
       </c>
-      <c r="F47" s="43" t="n">
-        <v>45024</v>
-      </c>
-      <c r="G47" s="43" t="n">
-        <v>45755</v>
-      </c>
-      <c r="H47" s="47" t="inlineStr">
-        <is>
-          <t>% of managed spend</t>
-        </is>
+      <c r="F47" s="35" t="n">
+        <v>45130</v>
+      </c>
+      <c r="G47" s="35" t="n">
+        <v>45861</v>
+      </c>
+      <c r="H47" s="46" t="n">
+        <v>1800</v>
       </c>
       <c r="I47" s="37" t="inlineStr">
         <is>
           <t>Transitioned</t>
         </is>
       </c>
-      <c r="J47" s="45" t="inlineStr">
+      <c r="J47" s="38" t="inlineStr">
         <is>
           <t>Ongoing under Thornfield standard billing.</t>
         </is>
@@ -2569,12 +2945,12 @@
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="31" t="inlineStr">
         <is>
-          <t>CUST-2025-0210</t>
+          <t>CUST-2025-0228</t>
         </is>
       </c>
       <c r="B48" s="32" t="inlineStr">
         <is>
-          <t>Blackthorn Reagent Systems</t>
+          <t>Havershaw Molecular</t>
         </is>
       </c>
       <c r="C48" s="33" t="inlineStr">
@@ -2584,838 +2960,507 @@
       </c>
       <c r="D48" s="34" t="inlineStr">
         <is>
+          <t>Katya Ovaskainen</t>
+        </is>
+      </c>
+      <c r="E48" s="34" t="inlineStr">
+        <is>
+          <t>Cyrus Delacroix</t>
+        </is>
+      </c>
+      <c r="F48" s="35" t="n">
+        <v>44930</v>
+      </c>
+      <c r="G48" s="35" t="n">
+        <v>45661</v>
+      </c>
+      <c r="H48" s="46" t="n">
+        <v>7700</v>
+      </c>
+      <c r="I48" s="37" t="inlineStr">
+        <is>
+          <t>Transitioned</t>
+        </is>
+      </c>
+      <c r="J48" s="38" t="inlineStr">
+        <is>
+          <t>Ongoing under Thornfield standard billing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="31" t="inlineStr">
+        <is>
+          <t>CUST-2025-0234</t>
+        </is>
+      </c>
+      <c r="B49" s="32" t="inlineStr">
+        <is>
+          <t>Jessop Bioanalytics</t>
+        </is>
+      </c>
+      <c r="C49" s="33" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+      <c r="D49" s="34" t="inlineStr">
+        <is>
           <t>Nora Fitzhugh</t>
         </is>
       </c>
-      <c r="E48" s="34" t="inlineStr">
+      <c r="E49" s="34" t="inlineStr">
+        <is>
+          <t>Anika Whitworth</t>
+        </is>
+      </c>
+      <c r="F49" s="35" t="n">
+        <v>45117</v>
+      </c>
+      <c r="G49" s="35" t="n">
+        <v>45848</v>
+      </c>
+      <c r="H49" s="46" t="n">
+        <v>4900</v>
+      </c>
+      <c r="I49" s="37" t="inlineStr">
+        <is>
+          <t>Transitioned</t>
+        </is>
+      </c>
+      <c r="J49" s="38" t="inlineStr">
+        <is>
+          <t>Ongoing under Thornfield standard billing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="39" t="inlineStr">
+        <is>
+          <t>CUST-2025-0237</t>
+        </is>
+      </c>
+      <c r="B50" s="40" t="inlineStr">
+        <is>
+          <t>Kettlewell Diagnostics</t>
+        </is>
+      </c>
+      <c r="C50" s="41" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+      <c r="D50" s="42" t="inlineStr">
+        <is>
+          <t>Diego Prasetya</t>
+        </is>
+      </c>
+      <c r="E50" s="42" t="inlineStr">
+        <is>
+          <t>Reid Alderman</t>
+        </is>
+      </c>
+      <c r="F50" s="43" t="n">
+        <v>45212</v>
+      </c>
+      <c r="G50" s="43" t="n">
+        <v>45943</v>
+      </c>
+      <c r="H50" s="47" t="inlineStr">
+        <is>
+          <t>% of managed spend</t>
+        </is>
+      </c>
+      <c r="I50" s="37" t="inlineStr">
+        <is>
+          <t>Transitioned</t>
+        </is>
+      </c>
+      <c r="J50" s="45" t="inlineStr">
+        <is>
+          <t>Ongoing under Thornfield standard billing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="31" t="inlineStr">
+        <is>
+          <t>CUST-2025-0240</t>
+        </is>
+      </c>
+      <c r="B51" s="32" t="inlineStr">
+        <is>
+          <t>Ledbury Cell Systems</t>
+        </is>
+      </c>
+      <c r="C51" s="33" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+      <c r="D51" s="34" t="inlineStr">
+        <is>
+          <t>Katya Ovaskainen</t>
+        </is>
+      </c>
+      <c r="E51" s="34" t="inlineStr">
         <is>
           <t>Sofia Bergen</t>
         </is>
       </c>
-      <c r="F48" s="35" t="n">
-        <v>45118</v>
-      </c>
-      <c r="G48" s="35" t="n">
-        <v>45849</v>
-      </c>
-      <c r="H48" s="46" t="n">
-        <v>6900</v>
-      </c>
-      <c r="I48" s="37" t="inlineStr">
+      <c r="F51" s="35" t="n">
+        <v>44942</v>
+      </c>
+      <c r="G51" s="35" t="n">
+        <v>45673</v>
+      </c>
+      <c r="H51" s="46" t="n">
+        <v>5600</v>
+      </c>
+      <c r="I51" s="37" t="inlineStr">
         <is>
           <t>Transitioned</t>
         </is>
       </c>
-      <c r="J48" s="38" t="inlineStr">
+      <c r="J51" s="38" t="inlineStr">
         <is>
           <t>Ongoing under Thornfield standard billing.</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="22" customHeight="1">
-      <c r="A49" s="39" t="inlineStr">
-        <is>
-          <t>CUST-2025-0213</t>
-        </is>
-      </c>
-      <c r="B49" s="40" t="inlineStr">
-        <is>
-          <t>Coppergate Diagnostics</t>
-        </is>
-      </c>
-      <c r="C49" s="41" t="inlineStr">
-        <is>
-          <t>Inherited — Bramwell</t>
-        </is>
-      </c>
-      <c r="D49" s="42" t="inlineStr">
+    <row r="52" ht="22" customHeight="1">
+      <c r="A52" s="39" t="inlineStr">
+        <is>
+          <t>CUST-2025-0243</t>
+        </is>
+      </c>
+      <c r="B52" s="40" t="inlineStr">
+        <is>
+          <t>Marshgate Bioinstruments</t>
+        </is>
+      </c>
+      <c r="C52" s="41" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+      <c r="D52" s="42" t="inlineStr">
+        <is>
+          <t>Emeka Balogun</t>
+        </is>
+      </c>
+      <c r="E52" s="42" t="inlineStr">
+        <is>
+          <t>Cyrus Delacroix</t>
+        </is>
+      </c>
+      <c r="F52" s="43" t="n">
+        <v>45035</v>
+      </c>
+      <c r="G52" s="43" t="n">
+        <v>45766</v>
+      </c>
+      <c r="H52" s="47" t="inlineStr">
+        <is>
+          <t>% of managed spend</t>
+        </is>
+      </c>
+      <c r="I52" s="37" t="inlineStr">
+        <is>
+          <t>Transitioned</t>
+        </is>
+      </c>
+      <c r="J52" s="45" t="inlineStr">
+        <is>
+          <t>Ongoing under Thornfield standard billing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="31" t="inlineStr">
+        <is>
+          <t>CUST-2025-0246</t>
+        </is>
+      </c>
+      <c r="B53" s="32" t="inlineStr">
+        <is>
+          <t>Norcross Genomic Systems</t>
+        </is>
+      </c>
+      <c r="C53" s="33" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+      <c r="D53" s="34" t="inlineStr">
+        <is>
+          <t>Nora Fitzhugh</t>
+        </is>
+      </c>
+      <c r="E53" s="34" t="inlineStr">
+        <is>
+          <t>Vanessa Trotter</t>
+        </is>
+      </c>
+      <c r="F53" s="35" t="n">
+        <v>45129</v>
+      </c>
+      <c r="G53" s="35" t="n">
+        <v>45860</v>
+      </c>
+      <c r="H53" s="46" t="n">
+        <v>9400</v>
+      </c>
+      <c r="I53" s="37" t="inlineStr">
+        <is>
+          <t>Transitioned</t>
+        </is>
+      </c>
+      <c r="J53" s="38" t="inlineStr">
+        <is>
+          <t>Ongoing under Thornfield standard billing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="39" t="inlineStr">
+        <is>
+          <t>CUST-2025-0249</t>
+        </is>
+      </c>
+      <c r="B54" s="40" t="inlineStr">
+        <is>
+          <t>Oakfield Diagnostics</t>
+        </is>
+      </c>
+      <c r="C54" s="41" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+      <c r="D54" s="42" t="inlineStr">
         <is>
           <t>Diego Prasetya</t>
         </is>
       </c>
-      <c r="E49" s="42" t="inlineStr">
-        <is>
-          <t>Cyrus Delacroix</t>
-        </is>
-      </c>
-      <c r="F49" s="43" t="n">
-        <v>45213</v>
-      </c>
-      <c r="G49" s="43" t="n">
-        <v>45944</v>
-      </c>
-      <c r="H49" s="47" t="inlineStr">
+      <c r="E54" s="42" t="inlineStr">
+        <is>
+          <t>Anika Whitworth</t>
+        </is>
+      </c>
+      <c r="F54" s="43" t="n">
+        <v>45224</v>
+      </c>
+      <c r="G54" s="43" t="n">
+        <v>45955</v>
+      </c>
+      <c r="H54" s="47" t="inlineStr">
         <is>
           <t>% of managed spend</t>
         </is>
       </c>
-      <c r="I49" s="37" t="inlineStr">
+      <c r="I54" s="37" t="inlineStr">
         <is>
           <t>Transitioned</t>
         </is>
       </c>
-      <c r="J49" s="45" t="inlineStr">
+      <c r="J54" s="45" t="inlineStr">
         <is>
           <t>Ongoing under Thornfield standard billing.</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="22" customHeight="1">
-      <c r="A50" s="31" t="inlineStr">
-        <is>
-          <t>CUST-2025-0216</t>
-        </is>
-      </c>
-      <c r="B50" s="32" t="inlineStr">
-        <is>
-          <t>Drayton Cell Culture</t>
-        </is>
-      </c>
-      <c r="C50" s="33" t="inlineStr">
-        <is>
-          <t>Inherited — Bramwell</t>
-        </is>
-      </c>
-      <c r="D50" s="34" t="inlineStr">
+    <row r="55" ht="22" customHeight="1">
+      <c r="A55" s="31" t="inlineStr">
+        <is>
+          <t>CUST-2025-0252</t>
+        </is>
+      </c>
+      <c r="B55" s="32" t="inlineStr">
+        <is>
+          <t>Sedgewick Bioanalytics</t>
+        </is>
+      </c>
+      <c r="C55" s="33" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+      <c r="D55" s="34" t="inlineStr">
         <is>
           <t>Katya Ovaskainen</t>
         </is>
       </c>
-      <c r="E50" s="34" t="inlineStr">
-        <is>
-          <t>Vanessa Trotter</t>
-        </is>
-      </c>
-      <c r="F50" s="35" t="n">
-        <v>44943</v>
-      </c>
-      <c r="G50" s="35" t="n">
-        <v>45674</v>
-      </c>
-      <c r="H50" s="46" t="n">
-        <v>4400</v>
-      </c>
-      <c r="I50" s="37" t="inlineStr">
+      <c r="E55" s="34" t="inlineStr">
+        <is>
+          <t>Reid Alderman</t>
+        </is>
+      </c>
+      <c r="F55" s="35" t="n">
+        <v>44929</v>
+      </c>
+      <c r="G55" s="35" t="n">
+        <v>45660</v>
+      </c>
+      <c r="H55" s="46" t="n">
+        <v>4200</v>
+      </c>
+      <c r="I55" s="37" t="inlineStr">
         <is>
           <t>Transitioned</t>
         </is>
       </c>
-      <c r="J50" s="38" t="inlineStr">
+      <c r="J55" s="38" t="inlineStr">
         <is>
           <t>Ongoing under Thornfield standard billing.</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="22" customHeight="1">
-      <c r="A51" s="39" t="inlineStr">
-        <is>
-          <t>CUST-2025-0219</t>
-        </is>
-      </c>
-      <c r="B51" s="40" t="inlineStr">
-        <is>
-          <t>Everleigh Bioinstruments</t>
-        </is>
-      </c>
-      <c r="C51" s="41" t="inlineStr">
-        <is>
-          <t>Inherited — Bramwell</t>
-        </is>
-      </c>
-      <c r="D51" s="42" t="inlineStr">
+    <row r="56" ht="22" customHeight="1">
+      <c r="A56" s="39" t="inlineStr">
+        <is>
+          <t>CUST-2025-0255</t>
+        </is>
+      </c>
+      <c r="B56" s="40" t="inlineStr">
+        <is>
+          <t>Tanfield Diagnostics</t>
+        </is>
+      </c>
+      <c r="C56" s="41" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+      <c r="D56" s="42" t="inlineStr">
         <is>
           <t>Emeka Balogun</t>
         </is>
       </c>
-      <c r="E51" s="42" t="inlineStr">
-        <is>
-          <t>Anika Whitworth</t>
-        </is>
-      </c>
-      <c r="F51" s="43" t="n">
-        <v>45036</v>
-      </c>
-      <c r="G51" s="43" t="n">
-        <v>45767</v>
-      </c>
-      <c r="H51" s="47" t="inlineStr">
+      <c r="E56" s="42" t="inlineStr">
+        <is>
+          <t>Sofia Bergen</t>
+        </is>
+      </c>
+      <c r="F56" s="43" t="n">
+        <v>45022</v>
+      </c>
+      <c r="G56" s="43" t="n">
+        <v>45753</v>
+      </c>
+      <c r="H56" s="47" t="inlineStr">
         <is>
           <t>% of managed spend</t>
         </is>
       </c>
-      <c r="I51" s="37" t="inlineStr">
+      <c r="I56" s="37" t="inlineStr">
         <is>
           <t>Transitioned</t>
         </is>
       </c>
-      <c r="J51" s="45" t="inlineStr">
+      <c r="J56" s="45" t="inlineStr">
         <is>
           <t>Ongoing under Thornfield standard billing.</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="22" customHeight="1">
-      <c r="A52" s="31" t="inlineStr">
-        <is>
-          <t>CUST-2025-0222</t>
-        </is>
-      </c>
-      <c r="B52" s="32" t="inlineStr">
-        <is>
-          <t>Foxhaven Genomic Analytics</t>
-        </is>
-      </c>
-      <c r="C52" s="33" t="inlineStr">
-        <is>
-          <t>Inherited — Bramwell</t>
-        </is>
-      </c>
-      <c r="D52" s="34" t="inlineStr">
-        <is>
-          <t>Nora Fitzhugh</t>
-        </is>
-      </c>
-      <c r="E52" s="34" t="inlineStr">
-        <is>
-          <t>Reid Alderman</t>
-        </is>
-      </c>
-      <c r="F52" s="35" t="n">
-        <v>45130</v>
-      </c>
-      <c r="G52" s="35" t="n">
-        <v>45861</v>
-      </c>
-      <c r="H52" s="46" t="n">
-        <v>1800</v>
-      </c>
-      <c r="I52" s="37" t="inlineStr">
-        <is>
-          <t>Transitioned</t>
-        </is>
-      </c>
-      <c r="J52" s="38" t="inlineStr">
-        <is>
-          <t>Ongoing under Thornfield standard billing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="22" customHeight="1">
-      <c r="A53" s="39" t="inlineStr">
-        <is>
-          <t>CUST-2025-0225</t>
-        </is>
-      </c>
-      <c r="B53" s="40" t="inlineStr">
-        <is>
-          <t>Glenmore Diagnostics</t>
-        </is>
-      </c>
-      <c r="C53" s="41" t="inlineStr">
-        <is>
-          <t>Inherited — Bramwell</t>
-        </is>
-      </c>
-      <c r="D53" s="42" t="inlineStr">
-        <is>
-          <t>Diego Prasetya</t>
-        </is>
-      </c>
-      <c r="E53" s="42" t="inlineStr">
-        <is>
-          <t>Sofia Bergen</t>
-        </is>
-      </c>
-      <c r="F53" s="43" t="n">
-        <v>45200</v>
-      </c>
-      <c r="G53" s="43" t="n">
-        <v>45931</v>
-      </c>
-      <c r="H53" s="47" t="inlineStr">
-        <is>
-          <t>% of managed spend</t>
-        </is>
-      </c>
-      <c r="I53" s="37" t="inlineStr">
-        <is>
-          <t>Transitioned</t>
-        </is>
-      </c>
-      <c r="J53" s="45" t="inlineStr">
-        <is>
-          <t>Ongoing under Thornfield standard billing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="22" customHeight="1">
-      <c r="A54" s="31" t="inlineStr">
-        <is>
-          <t>CUST-2025-0228</t>
-        </is>
-      </c>
-      <c r="B54" s="32" t="inlineStr">
-        <is>
-          <t>Havershaw Molecular</t>
-        </is>
-      </c>
-      <c r="C54" s="33" t="inlineStr">
-        <is>
-          <t>Inherited — Bramwell</t>
-        </is>
-      </c>
-      <c r="D54" s="34" t="inlineStr">
-        <is>
-          <t>Katya Ovaskainen</t>
-        </is>
-      </c>
-      <c r="E54" s="34" t="inlineStr">
-        <is>
-          <t>Cyrus Delacroix</t>
-        </is>
-      </c>
-      <c r="F54" s="35" t="n">
-        <v>44930</v>
-      </c>
-      <c r="G54" s="35" t="n">
-        <v>45661</v>
-      </c>
-      <c r="H54" s="46" t="n">
-        <v>7700</v>
-      </c>
-      <c r="I54" s="37" t="inlineStr">
-        <is>
-          <t>Transitioned</t>
-        </is>
-      </c>
-      <c r="J54" s="38" t="inlineStr">
-        <is>
-          <t>Ongoing under Thornfield standard billing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="22" customHeight="1">
-      <c r="A55" s="39" t="inlineStr">
-        <is>
-          <t>CUST-2025-0231</t>
-        </is>
-      </c>
-      <c r="B55" s="40" t="inlineStr">
-        <is>
-          <t>Ivybridge Reagent Labs</t>
-        </is>
-      </c>
-      <c r="C55" s="41" t="inlineStr">
-        <is>
-          <t>Inherited — Bramwell</t>
-        </is>
-      </c>
-      <c r="D55" s="42" t="inlineStr">
-        <is>
-          <t>Emeka Balogun</t>
-        </is>
-      </c>
-      <c r="E55" s="42" t="inlineStr">
-        <is>
-          <t>Vanessa Trotter</t>
-        </is>
-      </c>
-      <c r="F55" s="43" t="n">
-        <v>45023</v>
-      </c>
-      <c r="G55" s="43" t="n">
-        <v>45754</v>
-      </c>
-      <c r="H55" s="47" t="inlineStr">
-        <is>
-          <t>% of managed spend</t>
-        </is>
-      </c>
-      <c r="I55" s="37" t="inlineStr">
-        <is>
-          <t>Transitioned</t>
-        </is>
-      </c>
-      <c r="J55" s="45" t="inlineStr">
-        <is>
-          <t>Ongoing under Thornfield standard billing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="22" customHeight="1">
-      <c r="A56" s="31" t="inlineStr">
-        <is>
-          <t>CUST-2025-0234</t>
-        </is>
-      </c>
-      <c r="B56" s="32" t="inlineStr">
-        <is>
-          <t>Jessop Bioanalytics</t>
-        </is>
-      </c>
-      <c r="C56" s="33" t="inlineStr">
-        <is>
-          <t>Inherited — Bramwell</t>
-        </is>
-      </c>
-      <c r="D56" s="34" t="inlineStr">
-        <is>
-          <t>Nora Fitzhugh</t>
-        </is>
-      </c>
-      <c r="E56" s="34" t="inlineStr">
-        <is>
-          <t>Anika Whitworth</t>
-        </is>
-      </c>
-      <c r="F56" s="35" t="n">
-        <v>45117</v>
-      </c>
-      <c r="G56" s="35" t="n">
-        <v>45848</v>
-      </c>
-      <c r="H56" s="46" t="n">
-        <v>4900</v>
-      </c>
-      <c r="I56" s="37" t="inlineStr">
-        <is>
-          <t>Transitioned</t>
-        </is>
-      </c>
-      <c r="J56" s="38" t="inlineStr">
-        <is>
-          <t>Ongoing under Thornfield standard billing.</t>
-        </is>
-      </c>
-    </row>
     <row r="57" ht="22" customHeight="1">
-      <c r="A57" s="39" t="inlineStr">
-        <is>
-          <t>CUST-2025-0237</t>
-        </is>
-      </c>
-      <c r="B57" s="40" t="inlineStr">
-        <is>
-          <t>Kettlewell Diagnostics</t>
-        </is>
-      </c>
-      <c r="C57" s="41" t="inlineStr">
-        <is>
-          <t>Inherited — Bramwell</t>
-        </is>
-      </c>
-      <c r="D57" s="42" t="inlineStr">
-        <is>
-          <t>Diego Prasetya</t>
-        </is>
-      </c>
-      <c r="E57" s="42" t="inlineStr">
-        <is>
-          <t>Reid Alderman</t>
-        </is>
-      </c>
-      <c r="F57" s="43" t="n">
-        <v>45212</v>
-      </c>
-      <c r="G57" s="43" t="n">
-        <v>45943</v>
-      </c>
-      <c r="H57" s="47" t="inlineStr">
-        <is>
-          <t>% of managed spend</t>
-        </is>
-      </c>
-      <c r="I57" s="37" t="inlineStr">
-        <is>
-          <t>Transitioned</t>
-        </is>
-      </c>
-      <c r="J57" s="45" t="inlineStr">
-        <is>
-          <t>Ongoing under Thornfield standard billing.</t>
-        </is>
-      </c>
+      <c r="A57" s="52" t="inlineStr">
+        <is>
+          <t>Log maintenance notes</t>
+        </is>
+      </c>
+      <c r="B57" s="53" t="n"/>
+      <c r="C57" s="53" t="n"/>
+      <c r="D57" s="53" t="n"/>
+      <c r="E57" s="53" t="n"/>
+      <c r="F57" s="53" t="n"/>
+      <c r="G57" s="53" t="n"/>
+      <c r="H57" s="53" t="n"/>
+      <c r="I57" s="53" t="n"/>
+      <c r="J57" s="53" t="n"/>
     </row>
     <row r="58" ht="22" customHeight="1">
-      <c r="A58" s="31" t="inlineStr">
-        <is>
-          <t>CUST-2025-0240</t>
-        </is>
-      </c>
-      <c r="B58" s="32" t="inlineStr">
-        <is>
-          <t>Ledbury Cell Systems</t>
-        </is>
-      </c>
-      <c r="C58" s="33" t="inlineStr">
-        <is>
-          <t>Inherited — Bramwell</t>
-        </is>
-      </c>
-      <c r="D58" s="34" t="inlineStr">
-        <is>
-          <t>Katya Ovaskainen</t>
-        </is>
-      </c>
-      <c r="E58" s="34" t="inlineStr">
-        <is>
-          <t>Sofia Bergen</t>
-        </is>
-      </c>
-      <c r="F58" s="35" t="n">
-        <v>44942</v>
-      </c>
-      <c r="G58" s="35" t="n">
-        <v>45673</v>
-      </c>
-      <c r="H58" s="46" t="n">
-        <v>5600</v>
-      </c>
-      <c r="I58" s="37" t="inlineStr">
-        <is>
-          <t>Transitioned</t>
-        </is>
-      </c>
-      <c r="J58" s="38" t="inlineStr">
-        <is>
-          <t>Ongoing under Thornfield standard billing.</t>
+      <c r="A58" s="54" t="inlineStr">
+        <is>
+          <t>• All rows carry account_origin = "Inherited — Bramwell" in the ERPNext Customer master, matching the tag applied at the 08/25/2025 migration cutover.</t>
         </is>
       </c>
     </row>
     <row r="59" ht="22" customHeight="1">
-      <c r="A59" s="39" t="inlineStr">
-        <is>
-          <t>CUST-2025-0243</t>
-        </is>
-      </c>
-      <c r="B59" s="40" t="inlineStr">
-        <is>
-          <t>Marshgate Bioinstruments</t>
-        </is>
-      </c>
-      <c r="C59" s="41" t="inlineStr">
-        <is>
-          <t>Inherited — Bramwell</t>
-        </is>
-      </c>
-      <c r="D59" s="42" t="inlineStr">
-        <is>
-          <t>Emeka Balogun</t>
-        </is>
-      </c>
-      <c r="E59" s="42" t="inlineStr">
-        <is>
-          <t>Cyrus Delacroix</t>
-        </is>
-      </c>
-      <c r="F59" s="43" t="n">
-        <v>45035</v>
-      </c>
-      <c r="G59" s="43" t="n">
-        <v>45766</v>
-      </c>
-      <c r="H59" s="47" t="inlineStr">
-        <is>
-          <t>% of managed spend</t>
-        </is>
-      </c>
-      <c r="I59" s="37" t="inlineStr">
-        <is>
-          <t>Transitioned</t>
-        </is>
-      </c>
-      <c r="J59" s="45" t="inlineStr">
-        <is>
-          <t>Ongoing under Thornfield standard billing.</t>
+      <c r="A59" s="54" t="inlineStr">
+        <is>
+          <t>• "Original Monthly Retainer" reflects the fee arrangement as signed under the pre-close Bramwell MSA. Percentage-based arrangements ("% of managed spend") are billed off the applicable rate schedule; flat-retainer arrangements are billed at the stated dollar amount.</t>
         </is>
       </c>
     </row>
     <row r="60" ht="22" customHeight="1">
-      <c r="A60" s="31" t="inlineStr">
-        <is>
-          <t>CUST-2025-0246</t>
-        </is>
-      </c>
-      <c r="B60" s="32" t="inlineStr">
-        <is>
-          <t>Norcross Genomic Systems</t>
-        </is>
-      </c>
-      <c r="C60" s="33" t="inlineStr">
-        <is>
-          <t>Inherited — Bramwell</t>
-        </is>
-      </c>
-      <c r="D60" s="34" t="inlineStr">
-        <is>
-          <t>Nora Fitzhugh</t>
-        </is>
-      </c>
-      <c r="E60" s="34" t="inlineStr">
-        <is>
-          <t>Vanessa Trotter</t>
-        </is>
-      </c>
-      <c r="F60" s="35" t="n">
-        <v>45129</v>
-      </c>
-      <c r="G60" s="35" t="n">
-        <v>45860</v>
-      </c>
-      <c r="H60" s="46" t="n">
-        <v>9400</v>
-      </c>
-      <c r="I60" s="37" t="inlineStr">
-        <is>
-          <t>Transitioned</t>
-        </is>
-      </c>
-      <c r="J60" s="38" t="inlineStr">
-        <is>
-          <t>Ongoing under Thornfield standard billing.</t>
+      <c r="A60" s="54" t="inlineStr">
+        <is>
+          <t>• Post-close ongoing billing for percentage-based accounts follows Thornfield's standard company-wide rate card. Legacy-account renewals are seated under the separate legacy-accounts renewal-rate schedule at their renewal date, not backdated.</t>
         </is>
       </c>
     </row>
     <row r="61" ht="22" customHeight="1">
-      <c r="A61" s="39" t="inlineStr">
-        <is>
-          <t>CUST-2025-0249</t>
-        </is>
-      </c>
-      <c r="B61" s="40" t="inlineStr">
-        <is>
-          <t>Oakfield Diagnostics</t>
-        </is>
-      </c>
-      <c r="C61" s="41" t="inlineStr">
-        <is>
-          <t>Inherited — Bramwell</t>
-        </is>
-      </c>
-      <c r="D61" s="42" t="inlineStr">
-        <is>
-          <t>Diego Prasetya</t>
-        </is>
-      </c>
-      <c r="E61" s="42" t="inlineStr">
-        <is>
-          <t>Anika Whitworth</t>
-        </is>
-      </c>
-      <c r="F61" s="43" t="n">
-        <v>45224</v>
-      </c>
-      <c r="G61" s="43" t="n">
-        <v>45955</v>
-      </c>
-      <c r="H61" s="47" t="inlineStr">
-        <is>
-          <t>% of managed spend</t>
-        </is>
-      </c>
-      <c r="I61" s="37" t="inlineStr">
-        <is>
-          <t>Transitioned</t>
-        </is>
-      </c>
-      <c r="J61" s="45" t="inlineStr">
-        <is>
-          <t>Ongoing under Thornfield standard billing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="22" customHeight="1">
-      <c r="A62" s="31" t="inlineStr">
-        <is>
-          <t>CUST-2025-0252</t>
-        </is>
-      </c>
-      <c r="B62" s="32" t="inlineStr">
-        <is>
-          <t>Sedgewick Bioanalytics</t>
-        </is>
-      </c>
-      <c r="C62" s="33" t="inlineStr">
-        <is>
-          <t>Inherited — Bramwell</t>
-        </is>
-      </c>
-      <c r="D62" s="34" t="inlineStr">
-        <is>
-          <t>Katya Ovaskainen</t>
-        </is>
-      </c>
-      <c r="E62" s="34" t="inlineStr">
-        <is>
-          <t>Reid Alderman</t>
-        </is>
-      </c>
-      <c r="F62" s="35" t="n">
-        <v>44929</v>
-      </c>
-      <c r="G62" s="35" t="n">
-        <v>45660</v>
-      </c>
-      <c r="H62" s="46" t="n">
-        <v>4200</v>
-      </c>
-      <c r="I62" s="37" t="inlineStr">
-        <is>
-          <t>Transitioned</t>
-        </is>
-      </c>
-      <c r="J62" s="38" t="inlineStr">
-        <is>
-          <t>Ongoing under Thornfield standard billing.</t>
-        </is>
-      </c>
-    </row>
+      <c r="A61" s="54" t="inlineStr">
+        <is>
+          <t>• Dates reflect original executed instruments and are for record-keeping purposes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="22" customHeight="1"/>
     <row r="63" ht="22" customHeight="1">
-      <c r="A63" s="39" t="inlineStr">
-        <is>
-          <t>CUST-2025-0255</t>
-        </is>
-      </c>
-      <c r="B63" s="40" t="inlineStr">
-        <is>
-          <t>Tanfield Diagnostics</t>
-        </is>
-      </c>
-      <c r="C63" s="41" t="inlineStr">
-        <is>
-          <t>Inherited — Bramwell</t>
-        </is>
-      </c>
-      <c r="D63" s="42" t="inlineStr">
-        <is>
-          <t>Emeka Balogun</t>
-        </is>
-      </c>
-      <c r="E63" s="42" t="inlineStr">
-        <is>
-          <t>Sofia Bergen</t>
-        </is>
-      </c>
-      <c r="F63" s="43" t="n">
-        <v>45022</v>
-      </c>
-      <c r="G63" s="43" t="n">
-        <v>45753</v>
-      </c>
-      <c r="H63" s="47" t="inlineStr">
-        <is>
-          <t>% of managed spend</t>
-        </is>
-      </c>
-      <c r="I63" s="37" t="inlineStr">
-        <is>
-          <t>Transitioned</t>
-        </is>
-      </c>
-      <c r="J63" s="45" t="inlineStr">
-        <is>
-          <t>Ongoing under Thornfield standard billing.</t>
-        </is>
-      </c>
+      <c r="A63" s="55" t="inlineStr">
+        <is>
+          <t>Sign-off</t>
+        </is>
+      </c>
+      <c r="B63" s="56" t="n"/>
+      <c r="C63" s="56" t="n"/>
+      <c r="D63" s="56" t="n"/>
+      <c r="E63" s="56" t="n"/>
+      <c r="F63" s="56" t="n"/>
+      <c r="G63" s="56" t="n"/>
+      <c r="H63" s="56" t="n"/>
+      <c r="I63" s="56" t="n"/>
+      <c r="J63" s="56" t="n"/>
     </row>
     <row r="64" ht="26" customHeight="1">
-      <c r="A64" s="52" t="inlineStr">
-        <is>
-          <t>Log maintenance notes</t>
-        </is>
-      </c>
-      <c r="B64" s="53" t="n"/>
-      <c r="C64" s="53" t="n"/>
-      <c r="D64" s="53" t="n"/>
-      <c r="E64" s="53" t="n"/>
-      <c r="F64" s="53" t="n"/>
-      <c r="G64" s="53" t="n"/>
-      <c r="H64" s="53" t="n"/>
-      <c r="I64" s="53" t="n"/>
-      <c r="J64" s="53" t="n"/>
+      <c r="A64" s="57" t="inlineStr">
+        <is>
+          <t>Prepared and maintained by:</t>
+        </is>
+      </c>
+      <c r="B64" s="58" t="inlineStr">
+        <is>
+          <t>Sofia Bergen, Director, Client Strategy</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="22" customHeight="1">
-      <c r="A65" s="54" t="inlineStr">
-        <is>
-          <t>• All rows carry account_origin = "Inherited — Bramwell" in the ERPNext Customer master, matching the tag applied at the 08/25/2025 migration cutover.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="22" customHeight="1">
-      <c r="A66" s="54" t="inlineStr">
-        <is>
-          <t>• "Original Monthly Retainer" reflects the fee arrangement as signed under the pre-close Bramwell MSA. Percentage-based arrangements ("% of managed spend") are billed off the applicable rate schedule; flat-retainer arrangements are billed at the stated dollar amount.</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="22" customHeight="1">
-      <c r="A67" s="54" t="inlineStr">
-        <is>
-          <t>• Post-close ongoing billing for percentage-based accounts follows Thornfield's standard company-wide rate card. Legacy-account renewals are seated under the separate legacy-accounts renewal-rate schedule at their renewal date, not backdated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="22" customHeight="1">
-      <c r="A68" s="54" t="inlineStr">
-        <is>
-          <t>• Dates reflect original executed instruments and are for record-keeping purposes.</t>
-        </is>
-      </c>
-    </row>
+      <c r="A65" s="57" t="inlineStr">
+        <is>
+          <t>Last updated:</t>
+        </is>
+      </c>
+      <c r="B65" s="58" t="inlineStr">
+        <is>
+          <t>01/12/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="22" customHeight="1"/>
+    <row r="67" ht="22" customHeight="1"/>
+    <row r="68" ht="22" customHeight="1"/>
     <row r="69" ht="12" customHeight="1"/>
-    <row r="70" ht="24" customHeight="1">
-      <c r="A70" s="55" t="inlineStr">
-        <is>
-          <t>Sign-off</t>
-        </is>
-      </c>
-      <c r="B70" s="56" t="n"/>
-      <c r="C70" s="56" t="n"/>
-      <c r="D70" s="56" t="n"/>
-      <c r="E70" s="56" t="n"/>
-      <c r="F70" s="56" t="n"/>
-      <c r="G70" s="56" t="n"/>
-      <c r="H70" s="56" t="n"/>
-      <c r="I70" s="56" t="n"/>
-      <c r="J70" s="56" t="n"/>
-    </row>
-    <row r="71" ht="20" customHeight="1">
-      <c r="A71" s="57" t="inlineStr">
-        <is>
-          <t>Prepared and maintained by:</t>
-        </is>
-      </c>
-      <c r="B71" s="58" t="inlineStr">
-        <is>
-          <t>Sofia Bergen, Director, Client Strategy</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="20" customHeight="1">
-      <c r="A72" s="57" t="inlineStr">
-        <is>
-          <t>Last updated:</t>
-        </is>
-      </c>
-      <c r="B72" s="58" t="inlineStr">
-        <is>
-          <t>01/12/2026</t>
-        </is>
-      </c>
-    </row>
+    <row r="70" ht="24" customHeight="1"/>
+    <row r="71" ht="20" customHeight="1"/>
+    <row r="72" ht="20" customHeight="1"/>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="5">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="B3:J3"/>
-    <mergeCell ref="A32:J32"/>
     <mergeCell ref="B5:J5"/>
-    <mergeCell ref="A31:J31"/>
-    <mergeCell ref="B37:J37"/>
-    <mergeCell ref="B36:J36"/>
-    <mergeCell ref="A30:J30"/>
-    <mergeCell ref="A29:J29"/>
-    <mergeCell ref="A35:J35"/>
-    <mergeCell ref="A33:J33"/>
     <mergeCell ref="B4:J4"/>
     <mergeCell ref="B2:J2"/>
   </mergeCells>
@@ -3429,7 +3474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C105"/>
+  <dimension ref="A1:C107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4609,7 +4654,7 @@
       </c>
       <c r="C72" s="34" t="inlineStr">
         <is>
-          <t>Inherited — Bramwell</t>
+          <t>Thornfield native</t>
         </is>
       </c>
     </row>
@@ -4660,7 +4705,7 @@
       </c>
       <c r="C75" s="42" t="inlineStr">
         <is>
-          <t>Inherited — Bramwell</t>
+          <t>Thornfield native</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4773,7 @@
       </c>
       <c r="C79" s="42" t="inlineStr">
         <is>
-          <t>Inherited — Bramwell</t>
+          <t>Thornfield native</t>
         </is>
       </c>
     </row>
@@ -4813,7 +4858,7 @@
       </c>
       <c r="C84" s="34" t="inlineStr">
         <is>
-          <t>Inherited — Bramwell</t>
+          <t>Thornfield native</t>
         </is>
       </c>
     </row>
@@ -4847,7 +4892,7 @@
       </c>
       <c r="C86" s="34" t="inlineStr">
         <is>
-          <t>Inherited — Bramwell</t>
+          <t>Thornfield native</t>
         </is>
       </c>
     </row>
@@ -4881,7 +4926,7 @@
       </c>
       <c r="C88" s="34" t="inlineStr">
         <is>
-          <t>Inherited — Bramwell</t>
+          <t>Thornfield native</t>
         </is>
       </c>
     </row>
@@ -4915,7 +4960,7 @@
       </c>
       <c r="C90" s="34" t="inlineStr">
         <is>
-          <t>Inherited — Bramwell</t>
+          <t>Thornfield native</t>
         </is>
       </c>
     </row>
@@ -5171,6 +5216,40 @@
       <c r="C105" s="42" t="inlineStr">
         <is>
           <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="77" t="inlineStr">
+        <is>
+          <t>CUST-2025-0134</t>
+        </is>
+      </c>
+      <c r="B106" s="78" t="inlineStr">
+        <is>
+          <t>Coleridge Biotech Marketing</t>
+        </is>
+      </c>
+      <c r="C106" s="79" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="80" t="inlineStr">
+        <is>
+          <t>CUST-2025-0296</t>
+        </is>
+      </c>
+      <c r="B107" s="81" t="inlineStr">
+        <is>
+          <t>Kestrel Biosciences</t>
+        </is>
+      </c>
+      <c r="C107" s="82" t="inlineStr">
+        <is>
+          <t>Thornfield native</t>
         </is>
       </c>
     </row>

--- a/filesystem/MarketingOps/Org/client_services_account_transition_log.xlsx
+++ b/filesystem/MarketingOps/Org/client_services_account_transition_log.xlsx
@@ -416,7 +416,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -640,6 +640,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1388,7 +1391,7 @@
       </c>
       <c r="B14" s="32" t="inlineStr">
         <is>
-          <t>Draymere Sciences</t>
+          <t>Draymoor Sciences</t>
         </is>
       </c>
       <c r="C14" s="33" t="inlineStr">
@@ -3474,7 +3477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C107"/>
+  <dimension ref="A1:C108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3518,1736 +3521,1743 @@
       <c r="B4" s="64" t="n"/>
       <c r="C4" s="65" t="n"/>
     </row>
-    <row r="5" ht="12" customHeight="1"/>
-    <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="66" t="inlineStr">
+    <row r="5" ht="12" customHeight="1">
+      <c r="A5" s="86" t="inlineStr">
+        <is>
+          <t>Scope note: this crosswalk lists every ERPNext Customer record carrying an account_origin flag, regardless of activity level or financial-reporting treatment. Bramwell_FY2025_standalone.xlsx is scoped narrower, to Bramwell-origin accounts with material standalone FY2025 revenue; the Client Services Org Chart is scoped to currently active, actively-managed accounts. Row counts across the three documents are not expected to match.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="26" customHeight="1"/>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="66" t="inlineStr">
         <is>
           <t>ERPNext Customer ID</t>
         </is>
       </c>
-      <c r="B6" s="67" t="inlineStr">
+      <c r="B7" s="67" t="inlineStr">
         <is>
           <t>Canonical Client Name</t>
         </is>
       </c>
-      <c r="C6" s="67" t="inlineStr">
+      <c r="C7" s="67" t="inlineStr">
         <is>
           <t>Account Origin</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="39" t="inlineStr">
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="39" t="inlineStr">
         <is>
           <t>CUST-2025-0004</t>
         </is>
       </c>
-      <c r="B7" s="40" t="inlineStr">
+      <c r="B8" s="40" t="inlineStr">
         <is>
           <t>Pennywell Life Sciences</t>
         </is>
       </c>
-      <c r="C7" s="42" t="inlineStr">
-        <is>
-          <t>Thornfield native</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="31" t="inlineStr">
+      <c r="C8" s="42" t="inlineStr">
+        <is>
+          <t>Thornfield native</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="31" t="inlineStr">
         <is>
           <t>CUST-2025-0006</t>
         </is>
       </c>
-      <c r="B8" s="32" t="inlineStr">
+      <c r="B9" s="32" t="inlineStr">
         <is>
           <t>Ravenshill Assay Group</t>
         </is>
       </c>
-      <c r="C8" s="34" t="inlineStr">
-        <is>
-          <t>Thornfield native</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="39" t="inlineStr">
+      <c r="C9" s="34" t="inlineStr">
+        <is>
+          <t>Thornfield native</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="39" t="inlineStr">
         <is>
           <t>CUST-2025-0007</t>
         </is>
       </c>
-      <c r="B9" s="40" t="inlineStr">
+      <c r="B10" s="40" t="inlineStr">
         <is>
           <t>Meridian Biosystems</t>
         </is>
       </c>
-      <c r="C9" s="42" t="inlineStr">
-        <is>
-          <t>Thornfield native</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="31" t="inlineStr">
+      <c r="C10" s="42" t="inlineStr">
+        <is>
+          <t>Thornfield native</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="31" t="inlineStr">
         <is>
           <t>CUST-2025-0011</t>
         </is>
       </c>
-      <c r="B10" s="32" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>Halstead Analytical</t>
         </is>
       </c>
-      <c r="C10" s="34" t="inlineStr">
-        <is>
-          <t>Thornfield native</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="39" t="inlineStr">
+      <c r="C11" s="34" t="inlineStr">
+        <is>
+          <t>Thornfield native</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="39" t="inlineStr">
         <is>
           <t>CUST-2025-0014</t>
         </is>
       </c>
-      <c r="B11" s="40" t="inlineStr">
+      <c r="B12" s="40" t="inlineStr">
         <is>
           <t>Fairview Reagents</t>
         </is>
       </c>
-      <c r="C11" s="42" t="inlineStr">
-        <is>
-          <t>Thornfield native</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="31" t="inlineStr">
+      <c r="C12" s="42" t="inlineStr">
+        <is>
+          <t>Thornfield native</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="31" t="inlineStr">
         <is>
           <t>CUST-2025-0016</t>
         </is>
       </c>
-      <c r="B12" s="32" t="inlineStr">
+      <c r="B13" s="32" t="inlineStr">
         <is>
           <t>Brackenwood Diagnostics</t>
         </is>
       </c>
-      <c r="C12" s="34" t="inlineStr">
-        <is>
-          <t>Thornfield native</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="39" t="inlineStr">
+      <c r="C13" s="34" t="inlineStr">
+        <is>
+          <t>Thornfield native</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="39" t="inlineStr">
         <is>
           <t>CUST-2025-0019</t>
         </is>
       </c>
-      <c r="B13" s="40" t="inlineStr">
+      <c r="B14" s="40" t="inlineStr">
         <is>
           <t>Silverbrook Bioscience</t>
         </is>
       </c>
-      <c r="C13" s="42" t="inlineStr">
-        <is>
-          <t>Thornfield native</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="31" t="inlineStr">
+      <c r="C14" s="42" t="inlineStr">
+        <is>
+          <t>Thornfield native</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="31" t="inlineStr">
         <is>
           <t>CUST-2025-0022</t>
         </is>
       </c>
-      <c r="B14" s="32" t="inlineStr">
+      <c r="B15" s="32" t="inlineStr">
         <is>
           <t>Ipswich Molecular</t>
         </is>
       </c>
-      <c r="C14" s="34" t="inlineStr">
-        <is>
-          <t>Thornfield native</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="39" t="inlineStr">
+      <c r="C15" s="34" t="inlineStr">
+        <is>
+          <t>Thornfield native</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="39" t="inlineStr">
         <is>
           <t>CUST-2025-0024</t>
         </is>
       </c>
-      <c r="B15" s="40" t="inlineStr">
+      <c r="B16" s="40" t="inlineStr">
         <is>
           <t>Beckhurst Pharma Services</t>
         </is>
       </c>
-      <c r="C15" s="68" t="inlineStr">
-        <is>
-          <t>(not in Q4 spend export)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="31" t="inlineStr">
+      <c r="C16" s="68" t="inlineStr">
+        <is>
+          <t>Thornfield native</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="31" t="inlineStr">
         <is>
           <t>CUST-2025-0025</t>
         </is>
       </c>
-      <c r="B16" s="32" t="inlineStr">
+      <c r="B17" s="32" t="inlineStr">
         <is>
           <t>Kettering Assay Labs</t>
         </is>
       </c>
-      <c r="C16" s="34" t="inlineStr">
-        <is>
-          <t>Thornfield native</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="39" t="inlineStr">
+      <c r="C17" s="34" t="inlineStr">
+        <is>
+          <t>Thornfield native</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="39" t="inlineStr">
         <is>
           <t>CUST-2025-0028</t>
         </is>
       </c>
-      <c r="B17" s="40" t="inlineStr">
+      <c r="B18" s="40" t="inlineStr">
         <is>
           <t>Prospect Cell Systems</t>
         </is>
       </c>
-      <c r="C17" s="42" t="inlineStr">
-        <is>
-          <t>Thornfield native</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="31" t="inlineStr">
+      <c r="C18" s="42" t="inlineStr">
+        <is>
+          <t>Thornfield native</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="31" t="inlineStr">
         <is>
           <t>CUST-2025-0031</t>
         </is>
       </c>
-      <c r="B18" s="32" t="inlineStr">
+      <c r="B19" s="32" t="inlineStr">
         <is>
           <t>Redcliff Bioinstruments</t>
         </is>
       </c>
-      <c r="C18" s="34" t="inlineStr">
-        <is>
-          <t>Thornfield native</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="39" t="inlineStr">
+      <c r="C19" s="34" t="inlineStr">
+        <is>
+          <t>Thornfield native</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="39" t="inlineStr">
         <is>
           <t>CUST-2025-0033</t>
         </is>
       </c>
-      <c r="B19" s="40" t="inlineStr">
+      <c r="B20" s="40" t="inlineStr">
         <is>
           <t>Marlstone Bioscience</t>
         </is>
       </c>
-      <c r="C19" s="42" t="inlineStr">
-        <is>
-          <t>Thornfield native</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="31" t="inlineStr">
+      <c r="C20" s="42" t="inlineStr">
+        <is>
+          <t>Thornfield native</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="31" t="inlineStr">
         <is>
           <t>CUST-2025-0037</t>
         </is>
       </c>
-      <c r="B20" s="32" t="inlineStr">
+      <c r="B21" s="32" t="inlineStr">
         <is>
           <t>Steeplechase Diagnostics</t>
         </is>
       </c>
-      <c r="C20" s="34" t="inlineStr">
-        <is>
-          <t>Thornfield native</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="39" t="inlineStr">
+      <c r="C21" s="34" t="inlineStr">
+        <is>
+          <t>Thornfield native</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="39" t="inlineStr">
         <is>
           <t>CUST-2025-0041</t>
         </is>
       </c>
-      <c r="B21" s="40" t="inlineStr">
+      <c r="B22" s="40" t="inlineStr">
         <is>
           <t>Kennebec Genomics</t>
         </is>
       </c>
-      <c r="C21" s="42" t="inlineStr">
-        <is>
-          <t>Thornfield native</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="31" t="inlineStr">
+      <c r="C22" s="42" t="inlineStr">
+        <is>
+          <t>Thornfield native</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="31" t="inlineStr">
         <is>
           <t>CUST-2025-0044</t>
         </is>
       </c>
-      <c r="B22" s="32" t="inlineStr">
+      <c r="B23" s="32" t="inlineStr">
         <is>
           <t>Cavendish Life Sciences</t>
         </is>
       </c>
-      <c r="C22" s="34" t="inlineStr">
-        <is>
-          <t>Thornfield native</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="39" t="inlineStr">
+      <c r="C23" s="34" t="inlineStr">
+        <is>
+          <t>Thornfield native</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="39" t="inlineStr">
         <is>
           <t>CUST-2025-0047</t>
         </is>
       </c>
-      <c r="B23" s="40" t="inlineStr">
+      <c r="B24" s="40" t="inlineStr">
         <is>
           <t>Weybridge Scientific</t>
         </is>
       </c>
-      <c r="C23" s="42" t="inlineStr">
-        <is>
-          <t>Thornfield native</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="31" t="inlineStr">
+      <c r="C24" s="42" t="inlineStr">
+        <is>
+          <t>Thornfield native</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="31" t="inlineStr">
         <is>
           <t>CUST-2025-0049</t>
         </is>
       </c>
-      <c r="B24" s="32" t="inlineStr">
+      <c r="B25" s="32" t="inlineStr">
         <is>
           <t>Trenton Labware</t>
         </is>
       </c>
-      <c r="C24" s="34" t="inlineStr">
-        <is>
-          <t>Thornfield native</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="39" t="inlineStr">
+      <c r="C25" s="34" t="inlineStr">
+        <is>
+          <t>Thornfield native</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="39" t="inlineStr">
         <is>
           <t>CUST-2025-0052</t>
         </is>
       </c>
-      <c r="B25" s="40" t="inlineStr">
+      <c r="B26" s="40" t="inlineStr">
         <is>
           <t>Ashcombe Diagnostics</t>
         </is>
       </c>
-      <c r="C25" s="42" t="inlineStr">
-        <is>
-          <t>Thornfield native</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="31" t="inlineStr">
+      <c r="C26" s="42" t="inlineStr">
+        <is>
+          <t>Thornfield native</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="31" t="inlineStr">
         <is>
           <t>CUST-2025-0056</t>
         </is>
       </c>
-      <c r="B26" s="32" t="inlineStr">
+      <c r="B27" s="32" t="inlineStr">
         <is>
           <t>Fenland Bioanalytics</t>
         </is>
       </c>
-      <c r="C26" s="34" t="inlineStr">
-        <is>
-          <t>Thornfield native</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="39" t="inlineStr">
+      <c r="C27" s="34" t="inlineStr">
+        <is>
+          <t>Thornfield native</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="39" t="inlineStr">
         <is>
           <t>CUST-2025-0059</t>
         </is>
       </c>
-      <c r="B27" s="40" t="inlineStr">
+      <c r="B28" s="40" t="inlineStr">
         <is>
           <t>Hollowridge Molecular</t>
         </is>
       </c>
-      <c r="C27" s="42" t="inlineStr">
-        <is>
-          <t>Thornfield native</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="31" t="inlineStr">
+      <c r="C28" s="42" t="inlineStr">
+        <is>
+          <t>Thornfield native</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="31" t="inlineStr">
         <is>
           <t>CUST-2025-0063</t>
         </is>
       </c>
-      <c r="B28" s="32" t="inlineStr">
+      <c r="B29" s="32" t="inlineStr">
         <is>
           <t>Palliser Diagnostics</t>
         </is>
       </c>
-      <c r="C28" s="34" t="inlineStr">
-        <is>
-          <t>Thornfield native</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="39" t="inlineStr">
+      <c r="C29" s="34" t="inlineStr">
+        <is>
+          <t>Thornfield native</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="39" t="inlineStr">
         <is>
           <t>CUST-2025-0066</t>
         </is>
       </c>
-      <c r="B29" s="40" t="inlineStr">
+      <c r="B30" s="40" t="inlineStr">
         <is>
           <t>Tavistock Bioimaging</t>
         </is>
       </c>
-      <c r="C29" s="42" t="inlineStr">
-        <is>
-          <t>Thornfield native</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="31" t="inlineStr">
+      <c r="C30" s="42" t="inlineStr">
+        <is>
+          <t>Thornfield native</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="31" t="inlineStr">
         <is>
           <t>CUST-2025-0067</t>
         </is>
       </c>
-      <c r="B30" s="32" t="inlineStr">
+      <c r="B31" s="32" t="inlineStr">
         <is>
           <t>Millbrook Assay Systems</t>
         </is>
       </c>
-      <c r="C30" s="68" t="inlineStr">
-        <is>
-          <t>(not in Q4 spend export)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="39" t="inlineStr">
+      <c r="C31" s="68" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="39" t="inlineStr">
         <is>
           <t>CUST-2025-0069</t>
         </is>
       </c>
-      <c r="B31" s="40" t="inlineStr">
+      <c r="B32" s="40" t="inlineStr">
         <is>
           <t>Wrenwood Reagent Systems</t>
         </is>
       </c>
-      <c r="C31" s="42" t="inlineStr">
-        <is>
-          <t>Thornfield native</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="31" t="inlineStr">
+      <c r="C32" s="42" t="inlineStr">
+        <is>
+          <t>Thornfield native</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="31" t="inlineStr">
         <is>
           <t>CUST-2025-0072</t>
         </is>
       </c>
-      <c r="B32" s="32" t="inlineStr">
+      <c r="B33" s="32" t="inlineStr">
         <is>
           <t>Pennington Cell Therapy</t>
         </is>
       </c>
-      <c r="C32" s="34" t="inlineStr">
-        <is>
-          <t>Thornfield native</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="39" t="inlineStr">
+      <c r="C33" s="34" t="inlineStr">
+        <is>
+          <t>Thornfield native</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="39" t="inlineStr">
         <is>
           <t>CUST-2025-0075</t>
         </is>
       </c>
-      <c r="B33" s="40" t="inlineStr">
+      <c r="B34" s="40" t="inlineStr">
         <is>
           <t>Cornhill Diagnostics</t>
         </is>
       </c>
-      <c r="C33" s="42" t="inlineStr">
-        <is>
-          <t>Thornfield native</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="31" t="inlineStr">
+      <c r="C34" s="42" t="inlineStr">
+        <is>
+          <t>Thornfield native</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="31" t="inlineStr">
         <is>
           <t>CUST-2025-0078</t>
         </is>
       </c>
-      <c r="B34" s="32" t="inlineStr">
+      <c r="B35" s="32" t="inlineStr">
         <is>
           <t>Roxwell Molecular Labs</t>
         </is>
       </c>
-      <c r="C34" s="34" t="inlineStr">
-        <is>
-          <t>Thornfield native</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="39" t="inlineStr">
+      <c r="C35" s="34" t="inlineStr">
+        <is>
+          <t>Thornfield native</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="39" t="inlineStr">
         <is>
           <t>CUST-2025-0081</t>
         </is>
       </c>
-      <c r="B35" s="40" t="inlineStr">
+      <c r="B36" s="40" t="inlineStr">
         <is>
           <t>Dunstan Bioanalytics</t>
         </is>
       </c>
-      <c r="C35" s="42" t="inlineStr">
-        <is>
-          <t>Thornfield native</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="31" t="inlineStr">
+      <c r="C36" s="42" t="inlineStr">
+        <is>
+          <t>Thornfield native</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="31" t="inlineStr">
         <is>
           <t>CUST-2025-0084</t>
         </is>
       </c>
-      <c r="B36" s="32" t="inlineStr">
+      <c r="B37" s="32" t="inlineStr">
         <is>
           <t>Braemar Life Sciences</t>
         </is>
       </c>
-      <c r="C36" s="34" t="inlineStr">
-        <is>
-          <t>Thornfield native</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="39" t="inlineStr">
+      <c r="C37" s="34" t="inlineStr">
+        <is>
+          <t>Thornfield native</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="39" t="inlineStr">
         <is>
           <t>CUST-2025-0088</t>
         </is>
       </c>
-      <c r="B37" s="40" t="inlineStr">
+      <c r="B38" s="40" t="inlineStr">
         <is>
           <t>Caldwell Diagnostics</t>
         </is>
       </c>
-      <c r="C37" s="42" t="inlineStr">
-        <is>
-          <t>Thornfield native</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="31" t="inlineStr">
+      <c r="C38" s="42" t="inlineStr">
+        <is>
+          <t>Thornfield native</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="31" t="inlineStr">
         <is>
           <t>CUST-2025-0091</t>
         </is>
       </c>
-      <c r="B38" s="32" t="inlineStr">
+      <c r="B39" s="32" t="inlineStr">
         <is>
           <t>Ellisborough Bioinstruments</t>
         </is>
       </c>
-      <c r="C38" s="34" t="inlineStr">
-        <is>
-          <t>Thornfield native</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="39" t="inlineStr">
+      <c r="C39" s="34" t="inlineStr">
+        <is>
+          <t>Thornfield native</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="39" t="inlineStr">
         <is>
           <t>CUST-2025-0094</t>
         </is>
       </c>
-      <c r="B39" s="40" t="inlineStr">
+      <c r="B40" s="40" t="inlineStr">
         <is>
           <t>Harewood Genomic Sciences</t>
         </is>
       </c>
-      <c r="C39" s="42" t="inlineStr">
-        <is>
-          <t>Thornfield native</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="31" t="inlineStr">
+      <c r="C40" s="42" t="inlineStr">
+        <is>
+          <t>Thornfield native</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="31" t="inlineStr">
         <is>
           <t>CUST-2025-0097</t>
         </is>
       </c>
-      <c r="B40" s="32" t="inlineStr">
+      <c r="B41" s="32" t="inlineStr">
         <is>
           <t>Newforge Diagnostics</t>
         </is>
       </c>
-      <c r="C40" s="34" t="inlineStr">
-        <is>
-          <t>Thornfield native</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="39" t="inlineStr">
+      <c r="C41" s="34" t="inlineStr">
+        <is>
+          <t>Thornfield native</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="39" t="inlineStr">
         <is>
           <t>CUST-2025-0100</t>
         </is>
       </c>
-      <c r="B41" s="40" t="inlineStr">
+      <c r="B42" s="40" t="inlineStr">
         <is>
           <t>Thoresby Cell Systems</t>
         </is>
       </c>
-      <c r="C41" s="42" t="inlineStr">
-        <is>
-          <t>Thornfield native</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="31" t="inlineStr">
+      <c r="C42" s="42" t="inlineStr">
+        <is>
+          <t>Thornfield native</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="31" t="inlineStr">
         <is>
           <t>CUST-2025-0103</t>
         </is>
       </c>
-      <c r="B42" s="32" t="inlineStr">
+      <c r="B43" s="32" t="inlineStr">
         <is>
           <t>Wolverton Bioimaging</t>
         </is>
       </c>
-      <c r="C42" s="34" t="inlineStr">
-        <is>
-          <t>Thornfield native</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="39" t="inlineStr">
+      <c r="C43" s="34" t="inlineStr">
+        <is>
+          <t>Thornfield native</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="39" t="inlineStr">
         <is>
           <t>CUST-2025-0106</t>
         </is>
       </c>
-      <c r="B43" s="40" t="inlineStr">
+      <c r="B44" s="40" t="inlineStr">
         <is>
           <t>Ashland Reagent Group</t>
         </is>
       </c>
-      <c r="C43" s="42" t="inlineStr">
-        <is>
-          <t>Thornfield native</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="31" t="inlineStr">
+      <c r="C44" s="42" t="inlineStr">
+        <is>
+          <t>Thornfield native</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="31" t="inlineStr">
         <is>
           <t>CUST-2025-0109</t>
         </is>
       </c>
-      <c r="B44" s="32" t="inlineStr">
+      <c r="B45" s="32" t="inlineStr">
         <is>
           <t>Danbury Molecular</t>
         </is>
       </c>
-      <c r="C44" s="34" t="inlineStr">
-        <is>
-          <t>Thornfield native</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="39" t="inlineStr">
+      <c r="C45" s="34" t="inlineStr">
+        <is>
+          <t>Thornfield native</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="39" t="inlineStr">
         <is>
           <t>CUST-2025-0111</t>
         </is>
       </c>
-      <c r="B45" s="40" t="inlineStr">
+      <c r="B46" s="40" t="inlineStr">
         <is>
           <t>Halston Molecular Diagnostics</t>
         </is>
       </c>
-      <c r="C45" s="68" t="inlineStr">
-        <is>
-          <t>(not in Q4 spend export)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="31" t="inlineStr">
+      <c r="C46" s="68" t="inlineStr">
+        <is>
+          <t>Thornfield native</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="31" t="inlineStr">
         <is>
           <t>CUST-2025-0112</t>
         </is>
       </c>
-      <c r="B46" s="32" t="inlineStr">
+      <c r="B47" s="32" t="inlineStr">
         <is>
           <t>Fircrest Assay</t>
         </is>
       </c>
-      <c r="C46" s="34" t="inlineStr">
-        <is>
-          <t>Thornfield native</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="39" t="inlineStr">
+      <c r="C47" s="34" t="inlineStr">
+        <is>
+          <t>Thornfield native</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="39" t="inlineStr">
         <is>
           <t>CUST-2025-0115</t>
         </is>
       </c>
-      <c r="B47" s="40" t="inlineStr">
+      <c r="B48" s="40" t="inlineStr">
         <is>
           <t>Milford Bioanalytics</t>
         </is>
       </c>
-      <c r="C47" s="42" t="inlineStr">
-        <is>
-          <t>Thornfield native</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="31" t="inlineStr">
+      <c r="C48" s="42" t="inlineStr">
+        <is>
+          <t>Thornfield native</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="31" t="inlineStr">
         <is>
           <t>CUST-2025-0118</t>
         </is>
       </c>
-      <c r="B48" s="32" t="inlineStr">
+      <c r="B49" s="32" t="inlineStr">
         <is>
           <t>Radstock Diagnostics</t>
         </is>
       </c>
-      <c r="C48" s="34" t="inlineStr">
-        <is>
-          <t>Thornfield native</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="39" t="inlineStr">
+      <c r="C49" s="34" t="inlineStr">
+        <is>
+          <t>Thornfield native</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="39" t="inlineStr">
         <is>
           <t>CUST-2025-0121</t>
         </is>
       </c>
-      <c r="B49" s="40" t="inlineStr">
+      <c r="B50" s="40" t="inlineStr">
         <is>
           <t>Southridge Bioinstruments</t>
         </is>
       </c>
-      <c r="C49" s="42" t="inlineStr">
-        <is>
-          <t>Thornfield native</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="31" t="inlineStr">
+      <c r="C50" s="42" t="inlineStr">
+        <is>
+          <t>Thornfield native</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="31" t="inlineStr">
         <is>
           <t>CUST-2025-0124</t>
         </is>
       </c>
-      <c r="B50" s="32" t="inlineStr">
+      <c r="B51" s="32" t="inlineStr">
         <is>
           <t>Verwood Genomics</t>
         </is>
       </c>
-      <c r="C50" s="34" t="inlineStr">
-        <is>
-          <t>Thornfield native</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="39" t="inlineStr">
+      <c r="C51" s="34" t="inlineStr">
+        <is>
+          <t>Thornfield native</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="39" t="inlineStr">
         <is>
           <t>CUST-2025-0127</t>
         </is>
       </c>
-      <c r="B51" s="40" t="inlineStr">
+      <c r="B52" s="40" t="inlineStr">
         <is>
           <t>Yarmouth Scientific</t>
         </is>
       </c>
-      <c r="C51" s="42" t="inlineStr">
-        <is>
-          <t>Thornfield native</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="31" t="inlineStr">
+      <c r="C52" s="42" t="inlineStr">
+        <is>
+          <t>Thornfield native</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="31" t="inlineStr">
         <is>
           <t>CUST-2025-0130</t>
         </is>
       </c>
-      <c r="B52" s="32" t="inlineStr">
+      <c r="B53" s="32" t="inlineStr">
         <is>
           <t>Belmont Assay Systems</t>
         </is>
       </c>
-      <c r="C52" s="34" t="inlineStr">
-        <is>
-          <t>Inherited — Bramwell</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="39" t="inlineStr">
+      <c r="C53" s="34" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="39" t="inlineStr">
         <is>
           <t>CUST-2025-0133</t>
         </is>
       </c>
-      <c r="B53" s="40" t="inlineStr">
+      <c r="B54" s="40" t="inlineStr">
         <is>
           <t>Chatfield Diagnostics</t>
         </is>
       </c>
-      <c r="C53" s="42" t="inlineStr">
-        <is>
-          <t>Inherited — Bramwell</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="31" t="inlineStr">
+      <c r="C54" s="42" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="31" t="inlineStr">
         <is>
           <t>CUST-2025-0136</t>
         </is>
       </c>
-      <c r="B54" s="32" t="inlineStr">
+      <c r="B55" s="32" t="inlineStr">
         <is>
           <t>Deepwater Bioanalytics</t>
         </is>
       </c>
-      <c r="C54" s="34" t="inlineStr">
-        <is>
-          <t>Inherited — Bramwell</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="39" t="inlineStr">
+      <c r="C55" s="34" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="39" t="inlineStr">
         <is>
           <t>CUST-2025-0138</t>
         </is>
       </c>
-      <c r="B55" s="40" t="inlineStr">
+      <c r="B56" s="40" t="inlineStr">
         <is>
           <t>Kingsley Molecular</t>
         </is>
       </c>
-      <c r="C55" s="68" t="inlineStr">
-        <is>
-          <t>(not in Q4 spend export)</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="31" t="inlineStr">
+      <c r="C56" s="68" t="inlineStr">
+        <is>
+          <t>Thornfield native</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="31" t="inlineStr">
         <is>
           <t>CUST-2025-0139</t>
         </is>
       </c>
-      <c r="B56" s="32" t="inlineStr">
+      <c r="B57" s="32" t="inlineStr">
         <is>
           <t>Elmswood Reagent Labs</t>
         </is>
       </c>
-      <c r="C56" s="34" t="inlineStr">
-        <is>
-          <t>Inherited — Bramwell</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="39" t="inlineStr">
+      <c r="C57" s="34" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="39" t="inlineStr">
         <is>
           <t>CUST-2025-0142</t>
         </is>
       </c>
-      <c r="B57" s="40" t="inlineStr">
+      <c r="B58" s="40" t="inlineStr">
         <is>
           <t>Ashford Scientific Instruments</t>
         </is>
       </c>
-      <c r="C57" s="42" t="inlineStr">
-        <is>
-          <t>Inherited — Bramwell</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="31" t="inlineStr">
+      <c r="C58" s="42" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="31" t="inlineStr">
         <is>
           <t>CUST-2025-0145</t>
         </is>
       </c>
-      <c r="B58" s="32" t="inlineStr">
+      <c r="B59" s="32" t="inlineStr">
         <is>
           <t>Grantham Molecular Sciences</t>
         </is>
       </c>
-      <c r="C58" s="34" t="inlineStr">
-        <is>
-          <t>Inherited — Bramwell</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="39" t="inlineStr">
+      <c r="C59" s="34" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="39" t="inlineStr">
         <is>
           <t>CUST-2025-0146</t>
         </is>
       </c>
-      <c r="B59" s="40" t="inlineStr">
+      <c r="B60" s="40" t="inlineStr">
         <is>
           <t>Larkspur Diagnostics</t>
         </is>
       </c>
-      <c r="C59" s="68" t="inlineStr">
-        <is>
-          <t>(not in Q4 spend export)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="31" t="inlineStr">
+      <c r="C60" s="68" t="inlineStr">
+        <is>
+          <t>Thornfield native</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="31" t="inlineStr">
         <is>
           <t>CUST-2025-0148</t>
         </is>
       </c>
-      <c r="B60" s="32" t="inlineStr">
+      <c r="B61" s="32" t="inlineStr">
         <is>
           <t>Hemsworth Bioinstruments</t>
         </is>
       </c>
-      <c r="C60" s="34" t="inlineStr">
-        <is>
-          <t>Inherited — Bramwell</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="39" t="inlineStr">
+      <c r="C61" s="34" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="39" t="inlineStr">
         <is>
           <t>CUST-2025-0151</t>
         </is>
       </c>
-      <c r="B61" s="40" t="inlineStr">
+      <c r="B62" s="40" t="inlineStr">
         <is>
           <t>Ingleton Diagnostics</t>
         </is>
       </c>
-      <c r="C61" s="42" t="inlineStr">
-        <is>
-          <t>Inherited — Bramwell</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="20" customHeight="1">
-      <c r="A62" s="31" t="inlineStr">
+      <c r="C62" s="42" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="31" t="inlineStr">
         <is>
           <t>CUST-2025-0154</t>
         </is>
       </c>
-      <c r="B62" s="32" t="inlineStr">
+      <c r="B63" s="32" t="inlineStr">
         <is>
           <t>Jarrow Cell Culture Systems</t>
         </is>
       </c>
-      <c r="C62" s="34" t="inlineStr">
-        <is>
-          <t>Inherited — Bramwell</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="39" t="inlineStr">
+      <c r="C63" s="34" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="39" t="inlineStr">
         <is>
           <t>CUST-2025-0157</t>
         </is>
       </c>
-      <c r="B63" s="40" t="inlineStr">
+      <c r="B64" s="40" t="inlineStr">
         <is>
           <t>Northlake Bioinstruments</t>
         </is>
       </c>
-      <c r="C63" s="42" t="inlineStr">
-        <is>
-          <t>Inherited — Bramwell</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="20" customHeight="1">
-      <c r="A64" s="31" t="inlineStr">
+      <c r="C64" s="42" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="31" t="inlineStr">
         <is>
           <t>CUST-2025-0160</t>
         </is>
       </c>
-      <c r="B64" s="32" t="inlineStr">
+      <c r="B65" s="32" t="inlineStr">
         <is>
           <t>Kilbourne Genomics</t>
         </is>
       </c>
-      <c r="C64" s="34" t="inlineStr">
-        <is>
-          <t>Inherited — Bramwell</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="20" customHeight="1">
-      <c r="A65" s="39" t="inlineStr">
+      <c r="C65" s="34" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="39" t="inlineStr">
         <is>
           <t>CUST-2025-0163</t>
         </is>
       </c>
-      <c r="B65" s="40" t="inlineStr">
+      <c r="B66" s="40" t="inlineStr">
         <is>
           <t>Larchfield Bioanalytics</t>
         </is>
       </c>
-      <c r="C65" s="42" t="inlineStr">
-        <is>
-          <t>Inherited — Bramwell</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="20" customHeight="1">
-      <c r="A66" s="31" t="inlineStr">
+      <c r="C66" s="42" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="31" t="inlineStr">
         <is>
           <t>CUST-2025-0166</t>
         </is>
       </c>
-      <c r="B66" s="32" t="inlineStr">
+      <c r="B67" s="32" t="inlineStr">
         <is>
           <t>Marchmont Diagnostics</t>
         </is>
       </c>
-      <c r="C66" s="34" t="inlineStr">
-        <is>
-          <t>Inherited — Bramwell</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="20" customHeight="1">
-      <c r="A67" s="39" t="inlineStr">
+      <c r="C67" s="34" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="39" t="inlineStr">
         <is>
           <t>CUST-2025-0169</t>
         </is>
       </c>
-      <c r="B67" s="40" t="inlineStr">
+      <c r="B68" s="40" t="inlineStr">
         <is>
           <t>Norbury Bioimaging</t>
         </is>
       </c>
-      <c r="C67" s="42" t="inlineStr">
-        <is>
-          <t>Inherited — Bramwell</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="20" customHeight="1">
-      <c r="A68" s="31" t="inlineStr">
+      <c r="C68" s="42" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="31" t="inlineStr">
         <is>
           <t>CUST-2025-0172</t>
         </is>
       </c>
-      <c r="B68" s="32" t="inlineStr">
+      <c r="B69" s="32" t="inlineStr">
         <is>
           <t>Oakhurst Reagent Group</t>
         </is>
       </c>
-      <c r="C68" s="34" t="inlineStr">
-        <is>
-          <t>Inherited — Bramwell</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="20" customHeight="1">
-      <c r="A69" s="39" t="inlineStr">
+      <c r="C69" s="34" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="39" t="inlineStr">
         <is>
           <t>CUST-2025-0175</t>
         </is>
       </c>
-      <c r="B69" s="40" t="inlineStr">
+      <c r="B70" s="40" t="inlineStr">
         <is>
           <t>Portishead Molecular</t>
         </is>
       </c>
-      <c r="C69" s="42" t="inlineStr">
-        <is>
-          <t>Inherited — Bramwell</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="20" customHeight="1">
-      <c r="A70" s="31" t="inlineStr">
+      <c r="C70" s="42" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="31" t="inlineStr">
         <is>
           <t>CUST-2025-0178</t>
         </is>
       </c>
-      <c r="B70" s="32" t="inlineStr">
+      <c r="B71" s="32" t="inlineStr">
         <is>
           <t>Quenby Scientific Instruments</t>
         </is>
       </c>
-      <c r="C70" s="34" t="inlineStr">
-        <is>
-          <t>Inherited — Bramwell</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="20" customHeight="1">
-      <c r="A71" s="39" t="inlineStr">
+      <c r="C71" s="34" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="39" t="inlineStr">
         <is>
           <t>CUST-2025-0181</t>
         </is>
       </c>
-      <c r="B71" s="40" t="inlineStr">
+      <c r="B72" s="40" t="inlineStr">
         <is>
           <t>Ramsden Bioanalytics</t>
         </is>
       </c>
-      <c r="C71" s="42" t="inlineStr">
-        <is>
-          <t>Inherited — Bramwell</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="20" customHeight="1">
-      <c r="A72" s="31" t="inlineStr">
+      <c r="C72" s="42" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="31" t="inlineStr">
         <is>
           <t>CUST-2025-0184</t>
         </is>
       </c>
-      <c r="B72" s="32" t="inlineStr">
+      <c r="B73" s="32" t="inlineStr">
         <is>
           <t>Selwood Cell Systems</t>
         </is>
       </c>
-      <c r="C72" s="34" t="inlineStr">
-        <is>
-          <t>Thornfield native</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="20" customHeight="1">
-      <c r="A73" s="39" t="inlineStr">
+      <c r="C73" s="34" t="inlineStr">
+        <is>
+          <t>Thornfield native</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="39" t="inlineStr">
         <is>
           <t>CUST-2025-0187</t>
         </is>
       </c>
-      <c r="B73" s="40" t="inlineStr">
+      <c r="B74" s="40" t="inlineStr">
         <is>
           <t>Trentham Diagnostics</t>
         </is>
       </c>
-      <c r="C73" s="42" t="inlineStr">
-        <is>
-          <t>Inherited — Bramwell</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="20" customHeight="1">
-      <c r="A74" s="31" t="inlineStr">
+      <c r="C74" s="42" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="31" t="inlineStr">
         <is>
           <t>CUST-2025-0190</t>
         </is>
       </c>
-      <c r="B74" s="32" t="inlineStr">
+      <c r="B75" s="32" t="inlineStr">
         <is>
           <t>Ullswater Genomics</t>
         </is>
       </c>
-      <c r="C74" s="34" t="inlineStr">
-        <is>
-          <t>Inherited — Bramwell</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="20" customHeight="1">
-      <c r="A75" s="39" t="inlineStr">
+      <c r="C75" s="34" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="39" t="inlineStr">
         <is>
           <t>CUST-2025-0193</t>
         </is>
       </c>
-      <c r="B75" s="40" t="inlineStr">
+      <c r="B76" s="40" t="inlineStr">
         <is>
           <t>Vantage Bioinstruments</t>
         </is>
       </c>
-      <c r="C75" s="42" t="inlineStr">
-        <is>
-          <t>Thornfield native</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="20" customHeight="1">
-      <c r="A76" s="31" t="inlineStr">
+      <c r="C76" s="42" t="inlineStr">
+        <is>
+          <t>Thornfield native</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="31" t="inlineStr">
         <is>
           <t>CUST-2025-0196</t>
         </is>
       </c>
-      <c r="B76" s="32" t="inlineStr">
+      <c r="B77" s="32" t="inlineStr">
         <is>
           <t>Whitmore Assay Group</t>
         </is>
       </c>
-      <c r="C76" s="34" t="inlineStr">
-        <is>
-          <t>Inherited — Bramwell</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="20" customHeight="1">
-      <c r="A77" s="39" t="inlineStr">
+      <c r="C77" s="34" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="39" t="inlineStr">
         <is>
           <t>CUST-2025-0198</t>
         </is>
       </c>
-      <c r="B77" s="40" t="inlineStr">
+      <c r="B78" s="40" t="inlineStr">
         <is>
           <t>Fenwick Genomics</t>
         </is>
       </c>
-      <c r="C77" s="42" t="inlineStr">
-        <is>
-          <t>Inherited — Bramwell</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="20" customHeight="1">
-      <c r="A78" s="31" t="inlineStr">
+      <c r="C78" s="42" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="31" t="inlineStr">
         <is>
           <t>CUST-2025-0201</t>
         </is>
       </c>
-      <c r="B78" s="32" t="inlineStr">
+      <c r="B79" s="32" t="inlineStr">
         <is>
           <t>Wrenfield Scientific</t>
         </is>
       </c>
-      <c r="C78" s="34" t="inlineStr">
-        <is>
-          <t>Thornfield native</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="20" customHeight="1">
-      <c r="A79" s="39" t="inlineStr">
+      <c r="C79" s="34" t="inlineStr">
+        <is>
+          <t>Thornfield native</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="39" t="inlineStr">
         <is>
           <t>CUST-2025-0204</t>
         </is>
       </c>
-      <c r="B79" s="40" t="inlineStr">
+      <c r="B80" s="40" t="inlineStr">
         <is>
           <t>Yardley Molecular Diagnostics</t>
         </is>
       </c>
-      <c r="C79" s="42" t="inlineStr">
-        <is>
-          <t>Thornfield native</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="20" customHeight="1">
-      <c r="A80" s="31" t="inlineStr">
+      <c r="C80" s="42" t="inlineStr">
+        <is>
+          <t>Thornfield native</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="31" t="inlineStr">
         <is>
           <t>CUST-2025-0206</t>
         </is>
       </c>
-      <c r="B80" s="32" t="inlineStr">
+      <c r="B81" s="32" t="inlineStr">
         <is>
           <t>Marchmont Analytical Systems</t>
         </is>
       </c>
-      <c r="C80" s="68" t="inlineStr">
-        <is>
-          <t>(not in Q4 spend export)</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="20" customHeight="1">
-      <c r="A81" s="39" t="inlineStr">
+      <c r="C81" s="68" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82" s="39" t="inlineStr">
         <is>
           <t>CUST-2025-0207</t>
         </is>
       </c>
-      <c r="B81" s="40" t="inlineStr">
+      <c r="B82" s="40" t="inlineStr">
         <is>
           <t>Ainsworth Bioanalytics</t>
         </is>
       </c>
-      <c r="C81" s="42" t="inlineStr">
-        <is>
-          <t>Inherited — Bramwell</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="20" customHeight="1">
-      <c r="A82" s="31" t="inlineStr">
+      <c r="C82" s="42" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="31" t="inlineStr">
         <is>
           <t>CUST-2025-0208</t>
         </is>
       </c>
-      <c r="B82" s="32" t="inlineStr">
+      <c r="B83" s="32" t="inlineStr">
         <is>
           <t>Rothburn LabTech</t>
         </is>
       </c>
-      <c r="C82" s="68" t="inlineStr">
-        <is>
-          <t>(not in Q4 spend export)</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="20" customHeight="1">
-      <c r="A83" s="39" t="inlineStr">
+      <c r="C83" s="68" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="39" t="inlineStr">
         <is>
           <t>CUST-2025-0210</t>
         </is>
       </c>
-      <c r="B83" s="40" t="inlineStr">
+      <c r="B84" s="40" t="inlineStr">
         <is>
           <t>Blackthorn Reagent Systems</t>
         </is>
       </c>
-      <c r="C83" s="42" t="inlineStr">
-        <is>
-          <t>Inherited — Bramwell</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="20" customHeight="1">
-      <c r="A84" s="31" t="inlineStr">
+      <c r="C84" s="42" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="31" t="inlineStr">
         <is>
           <t>CUST-2025-0213</t>
         </is>
       </c>
-      <c r="B84" s="32" t="inlineStr">
+      <c r="B85" s="32" t="inlineStr">
         <is>
           <t>Coppergate Diagnostics</t>
         </is>
       </c>
-      <c r="C84" s="34" t="inlineStr">
-        <is>
-          <t>Thornfield native</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="20" customHeight="1">
-      <c r="A85" s="39" t="inlineStr">
+      <c r="C85" s="34" t="inlineStr">
+        <is>
+          <t>Thornfield native</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="20" customHeight="1">
+      <c r="A86" s="39" t="inlineStr">
         <is>
           <t>CUST-2025-0216</t>
         </is>
       </c>
-      <c r="B85" s="40" t="inlineStr">
+      <c r="B86" s="40" t="inlineStr">
         <is>
           <t>Drayton Cell Culture</t>
         </is>
       </c>
-      <c r="C85" s="42" t="inlineStr">
-        <is>
-          <t>Inherited — Bramwell</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="20" customHeight="1">
-      <c r="A86" s="31" t="inlineStr">
+      <c r="C86" s="42" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="31" t="inlineStr">
         <is>
           <t>CUST-2025-0219</t>
         </is>
       </c>
-      <c r="B86" s="32" t="inlineStr">
+      <c r="B87" s="32" t="inlineStr">
         <is>
           <t>Everleigh Bioinstruments</t>
         </is>
       </c>
-      <c r="C86" s="34" t="inlineStr">
-        <is>
-          <t>Thornfield native</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="20" customHeight="1">
-      <c r="A87" s="39" t="inlineStr">
+      <c r="C87" s="34" t="inlineStr">
+        <is>
+          <t>Thornfield native</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="39" t="inlineStr">
         <is>
           <t>CUST-2025-0222</t>
         </is>
       </c>
-      <c r="B87" s="40" t="inlineStr">
+      <c r="B88" s="40" t="inlineStr">
         <is>
           <t>Foxhaven Genomic Analytics</t>
         </is>
       </c>
-      <c r="C87" s="42" t="inlineStr">
-        <is>
-          <t>Inherited — Bramwell</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="20" customHeight="1">
-      <c r="A88" s="31" t="inlineStr">
+      <c r="C88" s="42" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="31" t="inlineStr">
         <is>
           <t>CUST-2025-0225</t>
         </is>
       </c>
-      <c r="B88" s="32" t="inlineStr">
+      <c r="B89" s="32" t="inlineStr">
         <is>
           <t>Glenmore Diagnostics</t>
         </is>
       </c>
-      <c r="C88" s="34" t="inlineStr">
-        <is>
-          <t>Thornfield native</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="20" customHeight="1">
-      <c r="A89" s="39" t="inlineStr">
+      <c r="C89" s="34" t="inlineStr">
+        <is>
+          <t>Thornfield native</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="39" t="inlineStr">
         <is>
           <t>CUST-2025-0228</t>
         </is>
       </c>
-      <c r="B89" s="40" t="inlineStr">
+      <c r="B90" s="40" t="inlineStr">
         <is>
           <t>Havershaw Molecular</t>
         </is>
       </c>
-      <c r="C89" s="42" t="inlineStr">
-        <is>
-          <t>Inherited — Bramwell</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="20" customHeight="1">
-      <c r="A90" s="31" t="inlineStr">
+      <c r="C90" s="42" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="31" t="inlineStr">
         <is>
           <t>CUST-2025-0231</t>
         </is>
       </c>
-      <c r="B90" s="32" t="inlineStr">
+      <c r="B91" s="32" t="inlineStr">
         <is>
           <t>Ivybridge Reagent Labs</t>
         </is>
       </c>
-      <c r="C90" s="34" t="inlineStr">
-        <is>
-          <t>Thornfield native</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="20" customHeight="1">
-      <c r="A91" s="39" t="inlineStr">
+      <c r="C91" s="34" t="inlineStr">
+        <is>
+          <t>Thornfield native</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="20" customHeight="1">
+      <c r="A92" s="39" t="inlineStr">
         <is>
           <t>CUST-2025-0234</t>
         </is>
       </c>
-      <c r="B91" s="40" t="inlineStr">
+      <c r="B92" s="40" t="inlineStr">
         <is>
           <t>Jessop Bioanalytics</t>
         </is>
       </c>
-      <c r="C91" s="42" t="inlineStr">
-        <is>
-          <t>Inherited — Bramwell</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="20" customHeight="1">
-      <c r="A92" s="31" t="inlineStr">
+      <c r="C92" s="42" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="31" t="inlineStr">
         <is>
           <t>CUST-2025-0237</t>
         </is>
       </c>
-      <c r="B92" s="32" t="inlineStr">
+      <c r="B93" s="32" t="inlineStr">
         <is>
           <t>Kettlewell Diagnostics</t>
         </is>
       </c>
-      <c r="C92" s="34" t="inlineStr">
-        <is>
-          <t>Inherited — Bramwell</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="20" customHeight="1">
-      <c r="A93" s="39" t="inlineStr">
+      <c r="C93" s="34" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="39" t="inlineStr">
         <is>
           <t>CUST-2025-0240</t>
         </is>
       </c>
-      <c r="B93" s="40" t="inlineStr">
+      <c r="B94" s="40" t="inlineStr">
         <is>
           <t>Ledbury Cell Systems</t>
         </is>
       </c>
-      <c r="C93" s="42" t="inlineStr">
-        <is>
-          <t>Inherited — Bramwell</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="20" customHeight="1">
-      <c r="A94" s="31" t="inlineStr">
+      <c r="C94" s="42" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="20" customHeight="1">
+      <c r="A95" s="31" t="inlineStr">
         <is>
           <t>CUST-2025-0243</t>
         </is>
       </c>
-      <c r="B94" s="32" t="inlineStr">
+      <c r="B95" s="32" t="inlineStr">
         <is>
           <t>Marshgate Bioinstruments</t>
         </is>
       </c>
-      <c r="C94" s="34" t="inlineStr">
-        <is>
-          <t>Inherited — Bramwell</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="20" customHeight="1">
-      <c r="A95" s="39" t="inlineStr">
+      <c r="C95" s="34" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="20" customHeight="1">
+      <c r="A96" s="39" t="inlineStr">
         <is>
           <t>CUST-2025-0246</t>
         </is>
       </c>
-      <c r="B95" s="40" t="inlineStr">
+      <c r="B96" s="40" t="inlineStr">
         <is>
           <t>Norcross Genomic Systems</t>
         </is>
       </c>
-      <c r="C95" s="42" t="inlineStr">
-        <is>
-          <t>Inherited — Bramwell</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="20" customHeight="1">
-      <c r="A96" s="31" t="inlineStr">
+      <c r="C96" s="42" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="20" customHeight="1">
+      <c r="A97" s="31" t="inlineStr">
         <is>
           <t>CUST-2025-0249</t>
         </is>
       </c>
-      <c r="B96" s="32" t="inlineStr">
+      <c r="B97" s="32" t="inlineStr">
         <is>
           <t>Oakfield Diagnostics</t>
         </is>
       </c>
-      <c r="C96" s="34" t="inlineStr">
-        <is>
-          <t>Inherited — Bramwell</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="20" customHeight="1">
-      <c r="A97" s="39" t="inlineStr">
+      <c r="C97" s="34" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="20" customHeight="1">
+      <c r="A98" s="39" t="inlineStr">
         <is>
           <t>CUST-2025-0252</t>
         </is>
       </c>
-      <c r="B97" s="40" t="inlineStr">
+      <c r="B98" s="40" t="inlineStr">
         <is>
           <t>Sedgewick Bioanalytics</t>
         </is>
       </c>
-      <c r="C97" s="42" t="inlineStr">
-        <is>
-          <t>Inherited — Bramwell</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="20" customHeight="1">
-      <c r="A98" s="31" t="inlineStr">
+      <c r="C98" s="42" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="20" customHeight="1">
+      <c r="A99" s="31" t="inlineStr">
         <is>
           <t>CUST-2025-0255</t>
         </is>
       </c>
-      <c r="B98" s="32" t="inlineStr">
+      <c r="B99" s="32" t="inlineStr">
         <is>
           <t>Tanfield Diagnostics</t>
         </is>
       </c>
-      <c r="C98" s="34" t="inlineStr">
-        <is>
-          <t>Inherited — Bramwell</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="20" customHeight="1">
-      <c r="A99" s="39" t="inlineStr">
+      <c r="C99" s="34" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="39" t="inlineStr">
         <is>
           <t>CUST-2025-0315</t>
         </is>
       </c>
-      <c r="B99" s="40" t="inlineStr">
+      <c r="B100" s="40" t="inlineStr">
         <is>
           <t>Sedgewick Life Sciences</t>
         </is>
       </c>
-      <c r="C99" s="42" t="inlineStr">
-        <is>
-          <t>Inherited — Bramwell</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="20" customHeight="1">
-      <c r="A100" s="31" t="inlineStr">
+      <c r="C100" s="42" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="20" customHeight="1">
+      <c r="A101" s="31" t="inlineStr">
         <is>
           <t>CUST-2025-0058</t>
         </is>
       </c>
-      <c r="B100" s="32" t="inlineStr">
+      <c r="B101" s="32" t="inlineStr">
         <is>
           <t>Petrichor Genomics</t>
         </is>
       </c>
-      <c r="C100" s="34" t="inlineStr">
-        <is>
-          <t>Thornfield native</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="20" customHeight="1">
-      <c r="A101" s="39" t="inlineStr">
+      <c r="C101" s="34" t="inlineStr">
+        <is>
+          <t>Thornfield native</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="20" customHeight="1">
+      <c r="A102" s="39" t="inlineStr">
         <is>
           <t>CUST-2025-0358</t>
         </is>
       </c>
-      <c r="B101" s="40" t="inlineStr">
+      <c r="B102" s="40" t="inlineStr">
         <is>
           <t>Kelbourne Diagnostics Reagents</t>
         </is>
       </c>
-      <c r="C101" s="42" t="inlineStr">
-        <is>
-          <t>Inherited — Bramwell</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="20" customHeight="1">
-      <c r="A102" s="31" t="inlineStr">
+      <c r="C102" s="42" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="31" t="inlineStr">
         <is>
           <t>CUST-2025-0331</t>
         </is>
       </c>
-      <c r="B102" s="32" t="inlineStr">
+      <c r="B103" s="32" t="inlineStr">
         <is>
           <t>Abersham Instruments</t>
         </is>
       </c>
-      <c r="C102" s="34" t="inlineStr">
-        <is>
-          <t>Inherited — Bramwell</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="20" customHeight="1">
-      <c r="A103" s="39" t="inlineStr">
+      <c r="C103" s="34" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="20" customHeight="1">
+      <c r="A104" s="39" t="inlineStr">
         <is>
           <t>CUST-2025-0344</t>
         </is>
       </c>
-      <c r="B103" s="40" t="inlineStr">
+      <c r="B104" s="40" t="inlineStr">
         <is>
           <t>Halewood Genomic Services</t>
         </is>
       </c>
-      <c r="C103" s="42" t="inlineStr">
-        <is>
-          <t>Inherited — Bramwell</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="20" customHeight="1">
-      <c r="A104" s="31" t="inlineStr">
+      <c r="C104" s="42" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="20" customHeight="1">
+      <c r="A105" s="31" t="inlineStr">
         <is>
           <t>CUST-2025-0375</t>
         </is>
       </c>
-      <c r="B104" s="32" t="inlineStr">
+      <c r="B105" s="32" t="inlineStr">
         <is>
           <t>Peartree Assay Labs</t>
         </is>
       </c>
-      <c r="C104" s="34" t="inlineStr">
-        <is>
-          <t>Inherited — Bramwell</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="20" customHeight="1">
-      <c r="A105" s="39" t="inlineStr">
+      <c r="C105" s="34" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="39" t="inlineStr">
         <is>
           <t>CUST-2025-0394</t>
         </is>
       </c>
-      <c r="B105" s="40" t="inlineStr">
-        <is>
-          <t>Draymere Sciences</t>
-        </is>
-      </c>
-      <c r="C105" s="42" t="inlineStr">
-        <is>
-          <t>Inherited — Bramwell</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="77" t="inlineStr">
+      <c r="B106" s="40" t="inlineStr">
+        <is>
+          <t>Draymoor Sciences</t>
+        </is>
+      </c>
+      <c r="C106" s="42" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="77" t="inlineStr">
         <is>
           <t>CUST-2025-0134</t>
         </is>
       </c>
-      <c r="B106" s="78" t="inlineStr">
+      <c r="B107" s="78" t="inlineStr">
         <is>
           <t>Coleridge Biotech Marketing</t>
         </is>
       </c>
-      <c r="C106" s="79" t="inlineStr">
-        <is>
-          <t>Inherited — Bramwell</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="80" t="inlineStr">
+      <c r="C107" s="79" t="inlineStr">
+        <is>
+          <t>Inherited — Bramwell</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="80" t="inlineStr">
         <is>
           <t>CUST-2025-0296</t>
         </is>
       </c>
-      <c r="B107" s="81" t="inlineStr">
+      <c r="B108" s="81" t="inlineStr">
         <is>
           <t>Kestrel Biosciences</t>
         </is>
       </c>
-      <c r="C107" s="82" t="inlineStr">
+      <c r="C108" s="82" t="inlineStr">
         <is>
           <t>Thornfield native</t>
         </is>

--- a/filesystem/MarketingOps/Org/client_services_account_transition_log.xlsx
+++ b/filesystem/MarketingOps/Org/client_services_account_transition_log.xlsx
@@ -3383,28 +3383,28 @@
       <c r="I57" s="53" t="n"/>
       <c r="J57" s="53" t="n"/>
     </row>
-    <row r="58" ht="22" customHeight="1">
+    <row r="58" ht="100" customHeight="1">
       <c r="A58" s="54" t="inlineStr">
         <is>
           <t>• All rows carry account_origin = "Inherited — Bramwell" in the ERPNext Customer master, matching the tag applied at the 08/25/2025 migration cutover.</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="22" customHeight="1">
+    <row r="59" ht="190" customHeight="1">
       <c r="A59" s="54" t="inlineStr">
         <is>
           <t>• "Original Monthly Retainer" reflects the fee arrangement as signed under the pre-close Bramwell MSA. Percentage-based arrangements ("% of managed spend") are billed off the applicable rate schedule; flat-retainer arrangements are billed at the stated dollar amount.</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="22" customHeight="1">
+    <row r="60" ht="165" customHeight="1">
       <c r="A60" s="54" t="inlineStr">
         <is>
           <t>• Post-close ongoing billing for percentage-based accounts follows Thornfield's standard company-wide rate card. Legacy-account renewals are seated under the separate legacy-accounts renewal-rate schedule at their renewal date, not backdated.</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="22" customHeight="1">
+    <row r="61" ht="65" customHeight="1">
       <c r="A61" s="54" t="inlineStr">
         <is>
           <t>• Dates reflect original executed instruments and are for record-keeping purposes.</t>

--- a/filesystem/MarketingOps/Org/client_services_account_transition_log.xlsx
+++ b/filesystem/MarketingOps/Org/client_services_account_transition_log.xlsx
@@ -3588,7 +3588,7 @@
       </c>
       <c r="B10" s="40" t="inlineStr">
         <is>
-          <t>Meridian Biosystems</t>
+          <t>Thistlewood Biosystems</t>
         </is>
       </c>
       <c r="C10" s="42" t="inlineStr">

--- a/filesystem/MarketingOps/Org/client_services_account_transition_log.xlsx
+++ b/filesystem/MarketingOps/Org/client_services_account_transition_log.xlsx
@@ -22,7 +22,7 @@
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
     <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -118,6 +118,12 @@
       <name val="Segoe UI"/>
       <i val="1"/>
       <color rgb="009A3412"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="FF475569"/>
       <sz val="9.5"/>
     </font>
   </fonts>
@@ -416,7 +422,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -643,6 +649,12 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1133,7 +1145,7 @@
       <c r="G8" s="35" t="n">
         <v>46092</v>
       </c>
-      <c r="H8" s="36" t="inlineStr">
+      <c r="H8" s="87" t="inlineStr">
         <is>
           <t>% of managed spend</t>
         </is>
@@ -1227,7 +1239,7 @@
       <c r="G10" s="35" t="n">
         <v>45914</v>
       </c>
-      <c r="H10" s="36" t="inlineStr">
+      <c r="H10" s="87" t="inlineStr">
         <is>
           <t>% of managed spend</t>
         </is>
@@ -1321,7 +1333,7 @@
       <c r="G12" s="35" t="n">
         <v>46053</v>
       </c>
-      <c r="H12" s="36" t="inlineStr">
+      <c r="H12" s="87" t="inlineStr">
         <is>
           <t>% of managed spend</t>
         </is>
@@ -1461,7 +1473,7 @@
       <c r="G15" s="43" t="n">
         <v>45975</v>
       </c>
-      <c r="H15" s="47" t="inlineStr">
+      <c r="H15" s="88" t="inlineStr">
         <is>
           <t>% of managed spend</t>
         </is>
@@ -1555,7 +1567,7 @@
       <c r="G17" s="43" t="n">
         <v>46126</v>
       </c>
-      <c r="H17" s="47" t="inlineStr">
+      <c r="H17" s="88" t="inlineStr">
         <is>
           <t>% of managed spend</t>
         </is>
@@ -1649,7 +1661,7 @@
       <c r="G19" s="43" t="n">
         <v>46188</v>
       </c>
-      <c r="H19" s="47" t="inlineStr">
+      <c r="H19" s="88" t="inlineStr">
         <is>
           <t>% of managed spend</t>
         </is>
@@ -1743,7 +1755,7 @@
       <c r="G21" s="43" t="n">
         <v>45996</v>
       </c>
-      <c r="H21" s="47" t="inlineStr">
+      <c r="H21" s="88" t="inlineStr">
         <is>
           <t>% of managed spend</t>
         </is>
@@ -1837,7 +1849,7 @@
       <c r="G23" s="43" t="n">
         <v>46142</v>
       </c>
-      <c r="H23" s="47" t="inlineStr">
+      <c r="H23" s="88" t="inlineStr">
         <is>
           <t>% of managed spend</t>
         </is>
@@ -1931,7 +1943,7 @@
       <c r="G25" s="43" t="n">
         <v>45961</v>
       </c>
-      <c r="H25" s="47" t="inlineStr">
+      <c r="H25" s="88" t="inlineStr">
         <is>
           <t>% of managed spend</t>
         </is>
@@ -2083,7 +2095,7 @@
       <c r="G29" s="43" t="n">
         <v>45808</v>
       </c>
-      <c r="H29" s="47" t="inlineStr">
+      <c r="H29" s="88" t="inlineStr">
         <is>
           <t>% of managed spend</t>
         </is>
@@ -2131,7 +2143,7 @@
       <c r="G30" s="35" t="n">
         <v>45909</v>
       </c>
-      <c r="H30" s="36" t="inlineStr">
+      <c r="H30" s="87" t="inlineStr">
         <is>
           <t>% of managed spend</t>
         </is>
@@ -2179,7 +2191,7 @@
       <c r="G31" s="43" t="n">
         <v>46036</v>
       </c>
-      <c r="H31" s="47" t="inlineStr">
+      <c r="H31" s="88" t="inlineStr">
         <is>
           <t>% of managed spend</t>
         </is>
@@ -2227,7 +2239,7 @@
       <c r="G32" s="35" t="n">
         <v>45980</v>
       </c>
-      <c r="H32" s="36" t="n">
+      <c r="H32" s="87" t="n">
         <v>5400</v>
       </c>
       <c r="I32" s="37" t="inlineStr">
@@ -2273,7 +2285,7 @@
       <c r="G33" s="43" t="n">
         <v>46081</v>
       </c>
-      <c r="H33" s="47" t="inlineStr">
+      <c r="H33" s="88" t="inlineStr">
         <is>
           <t>% of managed spend</t>
         </is>
@@ -2367,7 +2379,7 @@
       <c r="G35" s="43" t="n">
         <v>45873</v>
       </c>
-      <c r="H35" s="47" t="n">
+      <c r="H35" s="88" t="n">
         <v>4200</v>
       </c>
       <c r="I35" s="37" t="inlineStr">
@@ -2413,7 +2425,7 @@
       <c r="G36" s="35" t="n">
         <v>46121</v>
       </c>
-      <c r="H36" s="36" t="inlineStr">
+      <c r="H36" s="87" t="inlineStr">
         <is>
           <t>% of managed spend</t>
         </is>
@@ -2461,7 +2473,7 @@
       <c r="G37" s="43" t="n">
         <v>46002</v>
       </c>
-      <c r="H37" s="47" t="inlineStr">
+      <c r="H37" s="88" t="inlineStr">
         <is>
           <t>% of managed spend</t>
         </is>
@@ -2509,7 +2521,7 @@
       <c r="G38" s="35" t="n">
         <v>46073</v>
       </c>
-      <c r="H38" s="36" t="inlineStr">
+      <c r="H38" s="87" t="inlineStr">
         <is>
           <t>% of managed spend</t>
         </is>
@@ -2557,7 +2569,7 @@
       <c r="G39" s="43" t="n">
         <v>46235</v>
       </c>
-      <c r="H39" s="47" t="inlineStr">
+      <c r="H39" s="88" t="inlineStr">
         <is>
           <t>% of managed spend</t>
         </is>
@@ -2651,7 +2663,7 @@
       <c r="G41" s="35" t="n">
         <v>46247</v>
       </c>
-      <c r="H41" s="36" t="inlineStr">
+      <c r="H41" s="87" t="inlineStr">
         <is>
           <t>% of managed spend</t>
         </is>
@@ -2791,7 +2803,7 @@
       <c r="G44" s="43" t="n">
         <v>45755</v>
       </c>
-      <c r="H44" s="47" t="inlineStr">
+      <c r="H44" s="88" t="inlineStr">
         <is>
           <t>% of managed spend</t>
         </is>
@@ -3069,7 +3081,7 @@
       <c r="G50" s="43" t="n">
         <v>45943</v>
       </c>
-      <c r="H50" s="47" t="inlineStr">
+      <c r="H50" s="88" t="inlineStr">
         <is>
           <t>% of managed spend</t>
         </is>
@@ -3163,7 +3175,7 @@
       <c r="G52" s="43" t="n">
         <v>45766</v>
       </c>
-      <c r="H52" s="47" t="inlineStr">
+      <c r="H52" s="88" t="inlineStr">
         <is>
           <t>% of managed spend</t>
         </is>
@@ -3257,7 +3269,7 @@
       <c r="G54" s="43" t="n">
         <v>45955</v>
       </c>
-      <c r="H54" s="47" t="inlineStr">
+      <c r="H54" s="88" t="inlineStr">
         <is>
           <t>% of managed spend</t>
         </is>
@@ -3351,7 +3363,7 @@
       <c r="G56" s="43" t="n">
         <v>45753</v>
       </c>
-      <c r="H56" s="47" t="inlineStr">
+      <c r="H56" s="88" t="inlineStr">
         <is>
           <t>% of managed spend</t>
         </is>
